--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -45,7 +45,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -55,6 +55,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -421,13 +424,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B194"/>
+  <dimension ref="A1:B209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
-    <col width="203.77734375" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
-    <col width="8.88671875" customWidth="1" style="1" min="3" max="23"/>
-    <col width="8.88671875" customWidth="1" style="1" min="24" max="16384"/>
+    <col width="106.44140625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="8.88671875" customWidth="1" style="1" min="3" max="26"/>
+    <col width="8.88671875" customWidth="1" style="1" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" thickBot="1">
@@ -1939,7 +1942,7 @@
         </is>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="28.8" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
           <t>03/06/2026 14:57:32</t>
@@ -2916,10 +2919,8 @@
       </c>
     </row>
     <row r="194" ht="28.8" customHeight="1">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026 19:11:36</t>
-        </is>
+      <c r="A194" s="4" t="n">
+        <v>46272.79972222223</v>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
@@ -2932,7 +2933,292 @@
         </is>
       </c>
     </row>
-    <row r="195" ht="86.40000000000001" customHeight="1"/>
+    <row r="195" ht="86.40000000000001" customHeight="1">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>08/09/2026 20:14:36</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>[Buy For Me]
+• only tracking id's messages bot will send
+[Logistics]
+• Start Tsovinar telegram bot or automation system for "hertakan hamar"
+[Buy For Me]
+• if in the mail there are LILYA TADEVOSYAN name, then warn in the telegram bot message
+[Logistics]
+• finish the logistics automation workflow of trade gov am website
+[Logistics]
+• install the logistics automation in the agents pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="100.8" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026 20:00:35</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>[Buy For Me]
+• smoke tested all, everything works perfect, telegram bot sends message only when the tracking code is detected (and the specific name detected)
+[Logistics]
+• got new bugs, working on it. also changing the architecture of the output (xlsx to xls) and exel cells structure (column names, number, etc...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="86.40000000000001" customHeight="1">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>10/09/2026 18:51:07</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>[Logistics]
+• test the bug-fixed version of the trade.gov.am automation
+• fix the bugs and issues, and finish them
+[Buy For Me]
+• create a ui which will find some product's different prices in the same companies site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="158.4" customHeight="1">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026 20:03:42</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>[Logistics]
+• 1196 number check to make all the pages data points appear in the exel
+[Logistics]
+• install the new version of trade.gov.am to the agent's computer
+[Buy For Me]
+• create an API for the BFM articule searching for integration
+[ONEX-Academy]
+• use claude design to design very nice and bomb onex-like design for onex-academy</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="57.6" customHeight="1">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 19:05:17</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>[Buy For Me]
+• Changed supported countries to only am, de, gr, it, pl, es, ae, uk, and us; removed obsolete country markets; improved product-link parsing for Zara, H&amp;M, Puma, U.S. Polo, and Carpisa; added support for uspashop.com; expanded link validation tests; updated documentation and examples; committed and pushed all changes to main.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="187.2" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>17/09/2026 15:22:21</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>[DealFinder]
+• made these updates:
+  country , shop price, onex price, total price , the link of the product- these gonna be colums
+  show exchange with prices when mouse hovering
+  "dram" icon be at the right part of the price and smaller
+  show active shops logos (clicking them should go to the official site)
+  links be concrete
+  add weight column to product
+  one product priview
+  contrie choosing, excange rate sections delete
+[DealFinder]
+• add DealFinder project to Lovable</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="72" customHeight="1">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>23/09/2026 19:56:19</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>[ONEX-Academy]
+• fix the plane animation bugs (delays that are shown in the next page)
+[ONEX-Academy]
+• reduce the showing seconds in the Տերմիններ quiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="28.8" customHeight="1">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026 19:56:06</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>[ONEX-Academy]
+• make the cards with nice pictures, remove the onex@onex.am thing from the cards, make only ONEX maybe</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="86.40000000000001" customHeight="1">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>24/09/2026 17:59:13</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>[ONEX-Academy]
+• add new "customized quiz" specifically designed for one concrete agent.
+[ONEX-Academy]
+• flashcards game update
+• overall bug fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="72" customHeight="1">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026 16:50:53</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>[Blot]
+• start creating blot game with right rules
+[Blot]
+• make improvements, improve and correct scoring system, ui and other things that the player faces</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="72" customHeight="1">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>30/09/2026 17:02:49</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>[Blot]
+• update the gameplay and the score calculating system
+[cc-kpi-onex]
+• improved the visualisations and the overall ui and exel file correct parsing and handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="72" customHeight="1">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026 19:03:15</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>[cc-kpi-onex]
+• continue working on project
+[Blot]
+• make a website with domain
+[cc-kpi-onex]
+• make meeting with necessary people and get tasks, start working on them</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="259.2" customHeight="1">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>02/10/2026 19:58:55</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>[ai-agents-scores]
+• got the tasks from the quality control specialist and done them, here are what i have done:
+  ```
+  Added retry logic to handle timeout batches properly.
+  Exported and sanitized 5 n8n workflows and prompts, setting up automated secret redacting for backups.
+  Updated the live knowledge base with the latest tariffs, delivery/weight calculation rules, payment methods, and recalculations via the onex.am calculator.
+  Prepared 3 new evaluation criteria (Էմոջիներ, Կարեկցող խոսք, and Այլ բաժինների հետ հետևողականություն): drafted the prompts, added 6 new columns to the Supabase schema, prepared the Google
+  ```
+[Blot]
+• i have updated the ui of the game, made it crazy bomb nice ui with claude code, nice visualisations, etc...
+• i have updated and improved the blot player bot's logic and ai capabilities, now they make better decisions and play better.
+[ai-agents-scores]
+• made mcp with n8n-claude-supabase, so i can now just with one prompt make the necessary changes, which helps me to be more productive</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="409.6" customHeight="1">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>05/10/2026 18:35:51</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>[ai-agents-scores]
+1. Reviewing AI prompt improvements
+When you give feedback on a ticket, the AI now suggests a fix to its own instructions and grades the ticket again. Nothing changes until a person checks it.
+You see the old scores (green) next to the new ones (yellow), with the difference for each score.
+Approve puts the new instructions into use for all new tickets.
+Decline needs a reason; the AI then tries again using that reason.
+2. Feedback shows everywhere
+A ticket with feedback is now yellow and listed in Feedbacks everywhere, right after you send it.
+The feedback text is shown on the ticket and can be copied.
+"Finish &amp; Send Feedback" only appears when there is collected feedback that hasn't been sent.
+You can now also give feedback from the "View Graded Ticket" window.
+3. Manual changes are visible
+Scores changed by hand are outlined in purple and show the AI's original score.
+Criteria that got feedback are marked.
+A changed ticket level is marked too.
+Any change can be undone back to the AI's value.
+4. Changing a ticket's level
+Click the level badge (LEVEL 1/2/3) to change it.
+All averages, including the LEVEL 1 average, update right away.
+5. More accurate scores
+Averages no longer drift slightly because of rounding.
+A score change on one grading of a ticket no longer affects its other gradings.
+6. New Library section
+A place to store and edit team information: ONEX.am info, trainings, procedures.
+The ONEX.am part is pre-filled.
+7. AI Agents page
+The prompt that decides a ticket's level (1, 2 or 3) can now be viewed and edited there.
+8. Light mode
+A light/dark switch is in the sidebar.
+9. Languages
+English and Armenian texts were checked and fixed, and the parts that stayed in English now switch to Armenian too.
+10. Other fixes
+Some ticket dates were stored with day and month swapped; they are now correct.
+Status: Everything is tested. The latest changes (sections 3–8) are ready but not yet published to the live app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>06/10/2026 17:34:55</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>[Blot]
+• check the server's stored feedback
+[DealFinder]
+• Make the necessary updates on google extension
+[cc-kpi-onex]
+• implement the Kristina's tasks.
+[ai-agents-scores]
+• validate the results and tell Anna</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B209"/>
+  <dimension ref="A1:B210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
@@ -3064,7 +3064,9 @@
       <c r="B202" s="3" t="inlineStr">
         <is>
           <t>[ONEX-Academy]
-• make the cards with nice pictures, remove the onex@onex.am thing from the cards, make only ONEX maybe</t>
+• make the cards with nice pictures, remove the onex@onex.am thing from the cards, make only ONEX maybe
+[DealFinder]
+• continue working on the google extention</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3205,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>06/10/2026 17:34:55</t>
+          <t>06/10/2026 20:28:36</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -3215,7 +3217,25 @@
 [cc-kpi-onex]
 • implement the Kristina's tasks.
 [ai-agents-scores]
-• validate the results and tell Anna</t>
+• validate the results and tell Anna
+[cc-kpi-onex]
+• remove աշխատակից/ կարգ writtings from the ui, its too industrial, and not visual friendly.
+  improve the ui visuals of the upper part of the provided screenshot to be in the ui (do it right, and other motivation writtings)
+  add the levels (bronze silver gold ,etc..) nice visual friendly section with percent showing (shown in the new screenshot)
+  select in calendar the range of internship, so after that, the internship should be unchecked and the agent should become normal worker instead of intern. Also there should be editing function which admin can edit and make an internship worker standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>07/10/2026 19:45:36</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>[Blot]
+• add ai partner feature (ai agents that act like partners with user provided rules)</t>
         </is>
       </c>
     </row>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -3205,7 +3205,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>06/10/2026 20:28:36</t>
+          <t>06/10/2026 20:32:34</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -3222,20 +3222,27 @@
 • remove աշխատակից/ կարգ writtings from the ui, its too industrial, and not visual friendly.
   improve the ui visuals of the upper part of the provided screenshot to be in the ui (do it right, and other motivation writtings)
   add the levels (bronze silver gold ,etc..) nice visual friendly section with percent showing (shown in the new screenshot)
-  select in calendar the range of internship, so after that, the internship should be unchecked and the agent should become normal worker instead of intern. Also there should be editing function which admin can edit and make an internship worker standard.</t>
+  select in calendar the range of internship, so after that, the internship should be unchecked and the agent should become normal worker instead of intern. Also there should be editing function which admin can edit and make an internship worker standard.
+[Blot]
+• remove the line between baza-blot writting in every text, ui, logo, names, etc.. the users should only see it without the line</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>07/10/2026 19:45:36</t>
+          <t>07/10/2026 20:32:34</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
           <t>[Blot]
-• add ai partner feature (ai agents that act like partners with user provided rules)</t>
+• add ai partner feature (ai agents that act like partners with user provided rules)
+[Blot]
+• separate the xosal and xaxal types of rules of the ai partner , they should be separated from each other with maybe different tabs
+  when user clicks to the ai partner, make that more visual and engagig, so user should know that the default is just a bot named Ani, and that the new created ai partner isnt selected automatically.
+  when user selects the ai partner it isnt selecting in the game and in the game the 'Ani' plays, fix that so the ai should play using the corresponding users rules.
+  then user types rules make for the user nice items from the rules, so the rules should be separated.</t>
         </is>
       </c>
     </row>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-10980" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Reports" sheetId="1" state="visible" r:id="rId1"/>
@@ -45,9 +45,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -429,113 +432,113 @@
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
     <col width="106.44140625" customWidth="1" style="1" min="2" max="2"/>
-    <col width="8.88671875" customWidth="1" style="1" min="3" max="26"/>
-    <col width="8.88671875" customWidth="1" style="1" min="27" max="16384"/>
+    <col width="8.88671875" customWidth="1" style="1" min="3" max="27"/>
+    <col width="8.88671875" customWidth="1" style="1" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Date-Time</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Task Report</t>
         </is>
       </c>
     </row>
     <row r="2" ht="40.2" customHeight="1" thickBot="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>30/12/2025 17:47:58</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Created an AI agentic workflow with the main algorithm and correct logic: it takes a poor estimation together with an AI agent's prompt, improves the prompt, validates it (if it is still invalid, updates the prompt again and re-validates), and then rewrites the prompt.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40.2" customHeight="1" thickBot="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2026-05-01 17:36:08</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Created local Docker containers to run n8n, and added a new Telegram bot feature to the self-improving prompt workflow. Notifications are now sent when the prompt is updated, and the prompt is delivered as a text file by the bot to a specific user.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40.2" customHeight="1" thickBot="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-07-01 17:30:03</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Created a new n8n data table for the ticket analyzer agent's prompt, so that both the summary generator and estimator workflow and the self-improving prompt updater workflow access the same prompt, and updates apply to both workflows successfully.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28.8" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>08/01/2026 19:04:38</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Updated the Ticket Analyzer AI agent's workflow. It now sends the chat_history and ticket_id values to Supabase, as intended. Also continued working on the self-improving system, which will be completed tomorrow.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="57.6" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>09/01/2026 18:53:52</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Finished the self-improving workflow, so it now works with the production URL. Fixed the bug in the ticket analyzer agent's workflow, and started researching suitable, high-quality Armenian speech-to-text models (ElevenLabs, WAV.am, etc.). Also began creating an Armenian speech-to-text workflow to analyze and handle customer support calls.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="43.2" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>10/01/2026 14:12:45</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Created a new workflow that retrieves an audio file, sends it to WAV.am via an HTTP request to obtain the transcription, receives it back, and then structures the call transcription as a conversation between a customer and a call support agent. It works well, and the aim is to replicate it for chat support so that the same model can be used for analysis.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="43.2" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>12/01/2026 19:01:12</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Improved the speech-to-text n8n workflow, created and enhanced a new prompt for the extractor agent (the AI agent that structures call conversations), and ran tests of Armenian speech-to-text in order to benchmark the corresponding model.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="244.8" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>13/01/2026 18:38:04</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>1. Created a workflow that takes real support call audio (MP3), extracts the conversational text (structured as JSON, in the same format as support chats), and passes it to the next agent — the same agent that analyzes support chat tickets. The conversation is processed identically to the way the "ticket analyzer" handles support chat conversations. The workflow mirrors the chat analyzer and will eventually add a new column to Supabase with the same structure as in the chat ticket analyzing workflow. The only difference is the first stage, where the MP3 voice file is converted to text.
 2. Developed test cases and analyzed the results of the WAV.am speech-to-text model on real calls. Compiled a "model mistakes" text document detailing the errors observed. This document will be instrumental in building a robust AI agent system prompt, ensuring that the agent is aware of potential speech model inaccuracies and can correct them. Analyzed 18 calls, with 16 more still to benchmark, and requested additional calls (currently there are 34 call MP3 files).
@@ -545,12 +548,12 @@
       </c>
     </row>
     <row r="10" ht="86.40000000000001" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>14/01/2026 19:02:36</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Researched and became familiar with the Ladesk system, and created a new pipeline for sending audio files to n8n for processing. The system now automatically sends every resolved call ticket to n8n, where the corresponding call audio file is converted into Armenian text and then into a structured JSON message, similar to a support chat ticket.
 Also created a new rule in Ladesk to send call ticket JSON data to n8n, using the n8n API already configured in Ladesk.</t>
@@ -558,24 +561,24 @@
       </c>
     </row>
     <row r="11" ht="28.8" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>15/01/2026 17:46:12</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Resolved the issue of multiple calls within a single ticket in the n8n workflow, and corrected the Supabase row-adding node.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="129.6" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>16/01/2026 18:02:34</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Found a way to estimate call duration in n8n based on the audio file's byte size, header length, and similar details. This approach produces an approximate deviation of ±1–12 seconds from the actual call duration, and in my assessment this accuracy is acceptable and can be used.
 Calculated that, statistically, approximately 600–900 calls are resolved per day. At a later stage, will calculate the total aggregated call duration per day (or per month) in order to estimate the overall cost, for example when using WAV.am.
@@ -584,36 +587,36 @@
       </c>
     </row>
     <row r="13" ht="57.6" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>17/01/2026 13:22:08</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Summarized the speech-to-text model's mistakes. Based on that, performed prompt engineering and improved the model's extraction of call conversations. The model now extracts call conversations of better quality, which benefits the next step: an analyzer AI agent that produces high-quality estimations for the quality assurance of call support agents.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28.8" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>19/01/2026 18:13:08</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Improved the chat and call ticket analyzer workflows. They now add a "chat" or "call" status in the newly added status column in Supabase. Also ran a large number of tests and improved the call extractor agent's prompt.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="72" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>20/01/2026 18:38:23</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Tested and improved the support call extractor agent's prompt (taking its mistakes into account), and it now works well. Also created and implemented new methods for obtaining the number of currently active call tickets and the number of tickets resolved today, using n8n's HTTP Request and Code nodes.
 In addition, investigated LiveAgent's API documentation in order to implement all of these features.</t>
@@ -621,72 +624,72 @@
       </c>
     </row>
     <row r="16" ht="43.2" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>21/01/2026 18:24:31</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Created a new node chain in the n8n workflow to retrieve today's number of calls in the queue and the number of missed callbacks. Also investigated the GET/POST /ticket and GET /calls endpoints in the LiveAgent API documentation in order to implement this.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="72" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>22/01/2026 18:44:31</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Improved the overall performance and accuracy of the live call statistics display (in an n8n workflow, using LiveAgent API v3 calls and HTTP requests pipelined between n8n and Ladesk) for the upcoming statistics table. Also implemented precise calculation and display of today's call ticket statistics, including calls per hour, one call every X minutes, the number of ongoing calls, the number of calls in the queue, the number of calls resolved today, the number of calls missed today, and the number of missed calls that have been called back, among others.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="57.6" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>23/01/2026 22:46:25</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Replaced the standard "click to trigger" node with a webhook, including its URL, in the "call statistics sender" n8n workflow. This ensures that call statistics are sent to Lovable every X minutes through that webhook URL. Also added new statistics — average call duration and total call duration (a summary of all of today's calls) — and structured all of these statistics so that they can be retrieved and deployed easily.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="43.2" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>24/01/2026 14:00:26</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Created new statistics for the call center statistics n8n workflow, including the busiest call agent, call duration percentages, and the distribution of other insightful statistical values. Also received new tasks concerning chat agent performance and other chat statistics.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="57.6" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>26/01/2026 19:10:27</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Created and improved an n8n workflow that now sends new chat statistics (the number of agents busy in chat and their names as a list, and the number of chats in the queue) via HTTP request and webhook. Also changed "calls per X minutes" to "calls per X seconds", and received new tasks regarding call summary classification, WAV.am score spending statistics for calls, and caller number fixing.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="86.40000000000001" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>29/01/2026 18:40:24</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Created a new variable and calculated the score cost of transcribing an audio file with WAV.am, and created another new variable that retrieves the customer's phone number; fixed both variables.
 Currently working on a new AI agent that will take the chat or call (text version) together with the tags and produce a summary classification (it will choose one of the fixed summary classifications or, if the input does not correspond to any of them, suggest a new one).</t>
@@ -694,24 +697,24 @@
       </c>
     </row>
     <row r="22" ht="72" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>30/01/2026 17:56:01</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Fixed and brought to a deployable state the extraction of statistical figures from tickets — in particular the customer number, the cost of transcribing the support call audio (WAV.am score), and the trending summary, which first classifies the incoming ticket (chat or call history) so that the AI scoring system (or the new one, covering support calls only) can store the counts for each category and display the most trending topics for a given period. The counts are retrieved through the HTTP Request node that I created as an endpoint.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="144" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>31/01/2026 15:01:27</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Created several new data tables: one for the call and chat support center's statistics for the current day, and another for the history of each day (every day at 23:53 the figures are saved and reset to 0, ready for the next day's statistics).
 Improved the prompt of the statistical choice maker (the summarization analyst) AI agent, and improved and developed its workflows so that they work correctly in the call and chat support workflows separately (added new nodes to change, insert, get and write in n8n data tables, and so on, in order to implement all the logic). Also ran tests to fix errors and bugs in these workflows and to make the AI agent's prompt more stable and robust.
@@ -720,12 +723,12 @@
       </c>
     </row>
     <row r="24" ht="100.8" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>02/02/2026 19:16:21</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Created a new workflow that is triggered by a webhook and returns the trending topics, so that it can be connected to the AI Scoring site.
 Made changes to the LiveAgent and call ticket analyzer workflows: the system now checks whether a suggestion exists and, if it does, adds that suggestion to the newly created n8n data table; if there is no suggestion and the classifier AI agent decides to classify the ticket with one of the listed trending topics, the workflow continues in the usual way. This prevents the workflow from stopping or throwing errors caused by the existence of a suggestion or by an empty trending topic.</t>
@@ -733,12 +736,12 @@
       </c>
     </row>
     <row r="25" ht="72" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>03/02/2026 19:22:44</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Updated the list of trending topics in the classifier agent's prompt, improved the workflow to make it more robust, and performed prompt engineering on the AI summary classifier agent.
 Also received new tasks regarding the support agents' quality management AI estimation tools, as well as AI video-making prompt engineering tasks.</t>
@@ -746,12 +749,12 @@
       </c>
     </row>
     <row r="26" ht="72" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>04/02/2026 18:10:19</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Worked on generating videos for the tutorial phase of ONEX's support call center, which will be used to train new agents. Created several examples and discussed the results, which led to new tasks.
 Also checked n8n's "other topics" data table in order to identify topics that the AI classifier agent could not categorize, which means that it suggests adding them to the fixed list.</t>
@@ -759,12 +762,12 @@
       </c>
     </row>
     <row r="27" ht="57.6" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>05/02/2026 18:29:20</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Updated the AI classifier agent's prompt, adding a few new trending topics based on the AI's suggestions.
 Also updated and improved its workflow, which now sends the corresponding ticket ID for each newly suggested topic, so that I can see what kind of topic should be added to the fixed list.</t>
@@ -772,12 +775,12 @@
       </c>
     </row>
     <row r="28" ht="72" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>06/02/2026 20:38:32</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Received the necessary files containing the November, December and January data on support call center agents' quality (chat and call), and started working on the statistics drawer and the calculator workflow (or code).
 Also checked the "other trending topics" data table in n8n in order to create new trending topics, so that the AI classifier agent has these new options as well.</t>
@@ -785,12 +788,12 @@
       </c>
     </row>
     <row r="29" ht="57.6" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>07/02/2026 14:45:34</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Created code that parses the received Excel file into a structured CSV, which makes it possible to plot statistical and other graphs in order to visualize and analyze a specific agent's statistics, performance, and so on.
 Also wrote separate code and ran tests for plotting the statistics graphs.</t>
@@ -798,12 +801,12 @@
       </c>
     </row>
     <row r="30" ht="72" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>09/02/2026 21:38:14</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Created a new Streamlit project that makes it possible to select and compare the required agents in order to view their statistics.
 Also wrote code that reads the Excel data file and converts it into a fully structured and functional CSV file with clean, well-structured data.</t>
@@ -811,12 +814,12 @@
       </c>
     </row>
     <row r="31" ht="100.8" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>10/02/2026 19:31:09</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Developed a functional web platform that allows users to upload structured data files and receive automated statistical analysis and performance insights. The current version supports data ingestion and visualization, and further improvements and refinements are planned.
 In parallel, began designing and implementing new AI agents intended to evaluate service performance quality. These agents will analyze operational data and generate assessments based on predefined evaluation criteria. The focus is on building an automated, scalable system capable of consistent and objective performance analysis.</t>
@@ -824,12 +827,12 @@
       </c>
     </row>
     <row r="32" ht="100.8" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>11/02/2026 18:09:59</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Created new architectures for the "LiveAgent resolved tickets" and "call analyzer" n8n AI agentic workflows. The classifying AI agent in these workflows now takes the list of allowed trending topics from the data table, which makes it highly dynamic and flexible. As a result, when new trending topics are added to the data table based on the AI agent's suggestions, the list is updated automatically in the AI classifier agent's prompt in both n8n workflows.
 Also extracted the criteria from the customer support control call and chat agent statistics Excel file, and prepared to create AI agents that will perform the same rating for further statistics.</t>
@@ -837,24 +840,24 @@
       </c>
     </row>
     <row r="33" ht="72" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>12/02/2026 18:18:00</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Created two new n8n AI agents: an analyzer and a grader. The analyzer agent analyzes resolved tickets and passes its analysis to the grader agent, which then assigns grades and ratings for every provided criterion, along with a comment for each. All results are added to a neatly structured Google Sheet. Also improved the agents' prompts and generated valid, robust results, and added both agents and their parser code nodes to the chat analyzer n8n AI agentic workflow, where they work well.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="43.2" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>13/02/2026 17:56:15</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Updated the prompts of the grader and analyzer AI agents (based on the discussion with the quality support specialist).
 Added a new function that writes the name of the support service agent to the corresponding data point in the Google Sheet.</t>
@@ -862,12 +865,12 @@
       </c>
     </row>
     <row r="35" ht="115.2" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>14/02/2026 15:14:41</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Fixed an error in the Google Sheets node.
 Updated the system prompts of the analyzer and grader AI agents and the structure of the Google Sheets node.
@@ -877,12 +880,12 @@
       </c>
     </row>
     <row r="36" ht="129.6" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>16/02/2026 18:51:03</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Improved the AI call center agents' statistics and ratings website, creating a new data handling method and several new statistical features and visualizations (which significantly updated the UI, the frontend structure and the data handling).
 Created a new n8n AI workflow that sends data to this website, which visualizes all of it neatly and robustly.
@@ -892,12 +895,12 @@
       </c>
     </row>
     <row r="37" ht="43.2" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>17/02/2026 17:32:59</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Performed a major upgrade of the agents' AI scoring web interface.
 Added new features and made the colors nicer and richer, so that they correspond to the ONEX brand.</t>
@@ -905,12 +908,12 @@
       </c>
     </row>
     <row r="38" ht="144" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>18/02/2026 17:03:38</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Core features and logic
 Implemented ticket simulation logic for automatic ticket generation (intervals, hourly and weekly patterns) and peak hour analytics.
@@ -925,24 +928,24 @@
       </c>
     </row>
     <row r="39" ht="72" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>20/02/2026 18:41:22</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Implemented advanced ticket filtering with three case-insensitive searches (agent, ticket number and conversation), plus multi-select LEVEL 1/2/3 filtering, all combined with the date and agent filters in a single pipeline. Added conversation search coverage for both comments and chat history, and renamed "Raw Data" to "Tickets". Secured the app with login and logout, protected routes, and basic failed-attempt lockout and session handling, then verified everything with successful tests and a successful build.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="144" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>21/02/2026 16:01:11</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Added new evaluation criteria: chat start (yes/no) and need identified (yes/no); if a need exists but is not asked about → bad (1/0), proper handling → good (5), plus an empathy emoji or expression criterion (yes/no).
 Displayed the criteria grouped together in the Tickets section and applied fixed weights; if one of them is missing or null, its weight is redistributed across the remaining criteria.
@@ -954,48 +957,48 @@
       </c>
     </row>
     <row r="41" ht="72" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>23/02/2026 19:42:46</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Updated the AI agent scoring UI: refined the donut chart colors (greens for Excellent and Good) and redesigned cluster weight editing so that it is done per cluster through an Edit Weights modal instead of always-open fields. Weights are now edited as percentages, require a strict total of 100% per cluster, and can be applied either to the current ticket or to all tickets. Added "Today", "Yesterday", "Last week", "Last month" and "Reset" buttons to the date and time filtering section. Also started creating a new internet-searching AI workflow for the FPL Captain website.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>24/02/2026 20:46:30</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Implemented a per-agent ticket popup in Agent Details, so that every card can open all of the tickets for the selected agent.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28.8" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>25/02/2026 20:31:03</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Finished the AI Article Maker for FPL Captain, and improved the AI agents' system prompt and the image generator AI agent's prompt. Also had a long discussion with the CTO about future AI projects.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="57.6" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>26/02/2026 19:21:54</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Updated the list of trending topics in the n8n data tables, and updated the corresponding agent's prompt so that it now takes these topics into account as well.
 Also updated the sorting, filtering and searching algorithms of the AI Agents Scoring website.</t>
@@ -1003,12 +1006,12 @@
       </c>
     </row>
     <row r="45" ht="57.6" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>27/02/2026 19:24:46</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Updated the AI image generator prompt so that it generates the article's title text in the bottom-left part of the image.
 Updated the entire AI article maker n8n workflow: the article maker agent's prompt and the previous articles used in the prompt are now retrieved from the n8n data tables.</t>
@@ -1016,36 +1019,36 @@
       </c>
     </row>
     <row r="46" ht="28.8" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>28/02/2026 14:46:32</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Created the prototype of the Options Summarizer and comparison AI n8n workflow. Improved the agent's prompt and made the output valid CSV.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28.8" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>02/03/2026 22:42:08</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Updated the n8n workflow of the AI option summarizer. Currently working on making it handle as many documents as are sent to it through the webhook.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="57.6" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>03/03/2026 16:33:14</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Made updates to the AI option summarizer n8n workflow:
 Updated the AI summarizer agent's prompt, so the workflow now outputs neatly structured JSON instead of CSV.
@@ -1054,12 +1057,12 @@
       </c>
     </row>
     <row r="49" ht="57.6" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>04/03/2026 16:57:07</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Created a new n8n workflow for a self-improving agent system for the AI agents score site.
 Brought the n8n option summarizer workflow to a ready-to-test state, including a ready webhook URL, tested and working AI agents, and output processing, parsing and sending back.</t>
@@ -1067,12 +1070,12 @@
       </c>
     </row>
     <row r="50" ht="57.6" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>05/03/2026 14:58:40</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Created a new "bad" feedback button on the AI agents scoring site. When the button is used and a reason is written, the prompt is updated so that the AI agent can be upgraded and trained.
 Also started working on the n8n AI agent prompt self-improving workflow that handles this button.</t>
@@ -1080,336 +1083,336 @@
       </c>
     </row>
     <row r="51" ht="28.8" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>06/03/2026 17:20:06</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Improved the n8n AI self-improving workflow for prompt updating, validating and testing, in order to obtain the correct prompts. Also started working on retrieving the necessary ticket metadata to process and use in the n8n workflow.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28.8" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>07/03/2026 14:53:17</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Started working on the Dropify project for Georgia, which includes an n8n workflow with AI, website parsing, and an AI agent that will retrieve specific product prices.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>09/03/2026 15:02:59</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Researched site scraping for Dropify, including the different approaches available, their prices, and so on.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="43.2" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>10/03/2026 15:21:45</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>Published the n8n self-improving AI workflow, so that it receives calls while inactive, and updated the AI agents score website: clicking the new "bad" button and writing the reason now sends a call to the n8n workflow. Ran several tests; the workflow is in the testing state.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28.8" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>11/03/2026 14:54:12</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Continued working on the n8n AI self-improving workflow for the AI Agents Score project, and updated its prompt so that it corresponds to the prompt updating logic and is in the correct state.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28.8" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>12/03/2026 15:19:21</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Continued working on the n8n self-improving AI workflow. Started adding a new code node to parse the messages from the ticket data correctly.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28.8" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>13/03/2026 14:55:59</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Created a new data table in n8n and started connecting the tables in order to build correct pipelining for the self-improving agents of the AI agents scoring project, so that the prompts are updated correctly.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28.8" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>14/03/2026 15:55:52</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>Started working on the new delivery data in order to obtain coordinates from it, and began work on the future project for tracking deliveries.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28.8" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>16/03/2026 14:59:29</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Crafted a website for visualizing the delivery courier data points and the distances between them. Also wrote code to parse and pre-process the data and to extract coordinates from addresses.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>17/03/2026 15:14:44</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Researched the updated data points of the delivery courier data.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28.8" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>18/03/2026 15:04:10</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Met with the AI agents score users and instructed them to use the newly created self-improving workflow trigger button, named "Bad Response", in order to test it in further cases and make it ready for presentation and use.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28.8" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>19/03/2026 14:57:24</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Met with the Customer Support Quality Specialist and presented the new "Send Feedback" button, which is used to train the AI agents so that they start giving correct estimations and grades.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="43.2" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>20/03/2026 14:53:05</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Researched, deployed and tested several Armenian speech-to-text models from GitHub, with a view to adding them to the AI agents score system. Also received feedback on the AI grader and analyzer agent system from the head of quality control, and turned that feedback into tasks for the future.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="43.2" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>21/03/2026 15:02:00</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Reviewed the AI agents score requirements from the chat with the Head of Quality Control and developed the feedback form tasks. Implemented a new feature that allows users to submit feedback for the grader and analyzer agents several times per ticket. Updated all criteria names so that they align exactly with the Excel files, for consistency.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28.8" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>23/03/2026 14:51:15</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Ran tests and fixed bugs in the AI agents web analytics. Also received new feedback from the Head of Quality Control, turned it into tasks and completed them.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28.8" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>24/03/2026 14:48:58</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>Started creating the backend for the AI agents score website from scratch, because retrieving the data from Google Sheets every time is a very heavy and non-optimal process.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="28.8" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>25/03/2026 14:31:06</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Created a Supabase database table, uploaded the data to it, and started building an automatically updating n8n workflow, so that the website always has fresh data.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="28.8" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>26/03/2026 14:51:47</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Carried out a small piece of research into offline Telegram usage and bots in general. Also continued creating the backend database with PostgreSQL for the AI agents score website.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="28.8" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>27/03/2026 14:54:52</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Deployed successfully and integrated the backend database into the AI Agents Score website. It still needs some optimization and the integration of the paid database.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>28/03/2026 14:22:01</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>Successfully connected the backend to the paid Supabase Postgres database.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>30/03/2026 15:01:07</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>Continued creating the backend for the AI Agents Score website.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>31/03/2026 15:04:04</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>Started creating a workflow to automate some of the QA actions using Python and Bash commands.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>01/04/2026 14:57:22</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>Created QA automation code that automates the manual QA engineers' flow.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="28.8" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>02/04/2026 15:03:17</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>Researched and built several different cases for the QA automation project. Also built one case using another automated browser, and completed several tasks for the Quality Control department.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="28.8" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>03/04/2026 14:37:03</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>Received tasks from the Head of Quality Control and started working on them. Also completed several tasks on the QA automation, finishing the first part of the user registration phase.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="28.8" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>04/04/2026 14:40:30</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Updated the AI Agents Score website and optimized and improved the weights as required. Also continued the QA automation task — user email verification and the final registration phase.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="28.8" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>06/04/2026 15:06:41</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>Optimized and speeded up the data loading of the AI Agents Score website. Also made significant progress on the QA automation: it now creates a user, verifies the email and enters the user's bio data — only passport confirmation is left.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="43.2" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>07/04/2026 14:55:49</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>Made several attempts to improve the QA automation workflow.
 Also added a new "good" positive feedback feature (with the correct n8n webhook URL call) to the AI Agents Score website.</t>
@@ -1417,108 +1420,108 @@
       </c>
     </row>
     <row r="79" ht="28.8" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>08/04/2026 15:05:35</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>Finished the first QA automation project and deployed it on the QA team lead's computer, where it works perfectly. Also caught and fixed errors and made the code as robust as possible.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>09/04/2026 14:52:46</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>Cleaned up the QA automation code and made the flow clearer.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="28.8" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>10/04/2026 14:06:42</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>Updated the QA flow. It now handles failing cases more flexibly and avoids failures by reloading. Moving on to the next phases.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="28.8" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>11/04/2026 15:01:10</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>Received new tasks to automate the QA for next week and started working on them by adding new steps to the automation flow. Also added a large number of error catching and handling features.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="43.2" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>13/04/2026 14:38:54</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>Added a lot to the flow; only the created parcel validation is left in order to finish the QA automation flow, and work on it is in progress. The previously completed steps and improvements were fixed, committed, validated and made robust against errors.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="28.8" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>14/04/2026 14:37:45</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>Updated the QA automation flow and made it more robust for the user experience and for bad cases in general. One problem still remains to be fixed.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>15/04/2026 15:13:35</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>Deployed the backend for the AI Agents Score project with Supabase, and currently working on optimizing it.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="43.2" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>16/04/2026 14:41:37</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>Created a new data table in Supabase, and built the automatic workflow for data handling and the corresponding data pre-processing, which parses new data and adds it to the Supabase PostgreSQL database. It works perfectly. Also continued deploying the backend for the AI Agents Score AI-powered website that I created from scratch.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="57.6" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>17/04/2026 15:10:24</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>Successfully deployed the Supabase backend for the AI Agents Score website, so loading is now much faster. Also deleted unnecessary files, functions, graphs and variables related to the redundant graphs.
 Attended a meeting and received new tasks concerning ONEX Georgia.</t>
@@ -1526,12 +1529,12 @@
       </c>
     </row>
     <row r="88" ht="28.8" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>18/04/2026 13:24:35</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>Caught several errors and fixed bugs on the AI Agents Score website, tested the fixes and deployed the changes.
 Also received new tasks about the region and city input problem for the ONEX Georgia region, and started working on them.</t>
@@ -1539,12 +1542,12 @@
       </c>
     </row>
     <row r="89" ht="86.40000000000001" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>20/04/2026 14:57:53</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>Finished the QA automation flow with all of its cases, error handling and robust automated flow, and deployed it on the QA engineer's computer.
 Received new tasks about creating another automated QA flow.
@@ -1553,84 +1556,84 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>21/04/2026 15:01:59</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>Updated and finished the overall projects report and presentation, and received new tasks regarding the QA automation.</t>
         </is>
       </c>
     </row>
     <row r="91" ht="43.2" customHeight="1">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>22/04/2026 16:40:55</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>Visited the Merdzavan warehouse and attended a meeting with its CEO. Learned how they work with Excel files, and they demonstrated their work so that I can automate everything possible for them. Also received new tasks about that automation, along with materials that are to be sent to me.</t>
         </is>
       </c>
     </row>
     <row r="92" ht="28.8" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>23/04/2026 16:32:15</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>Received the tasks for the Merdzavan automation, documented them, created a roadmap with deadlines and started working on it. Also received the new materials needed for the work.</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>25/04/2026 14:56:48</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>Started creating the n8n AI workflow for the Merdzavan task, and researched different ways of implementing it.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="28.8" customHeight="1">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>27/04/2026 15:01:17</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>Continued crafting the AI n8n workflow for Merdzavan, and also performed manual data pre-processing for the AI agent's system prompt, which will be used in the same AI agent workflow.</t>
         </is>
       </c>
     </row>
     <row r="95" ht="28.8" customHeight="1">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>28/04/2026 15:05:48</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>Finished creating the main working phase of the n8n agentic AI workflow. Waiting for approval in order to continue with the Telegram bot implementation.</t>
         </is>
       </c>
     </row>
     <row r="96" ht="57.6" customHeight="1">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>29/04/2026 15:12:52</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>Almost finished the AI n8n workflow for the Merdzavan automation; only some tests on real data and deployment with the Telegram bot are left.
 Also received several tasks for further QA automation, and arranged a further meeting with the team leads and the CITO/CTO about integrating AI across the whole IT department (QA, backend team and frontend team).</t>
@@ -1638,168 +1641,168 @@
       </c>
     </row>
     <row r="97" ht="43.2" customHeight="1">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>30/04/2026 14:23:02</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>Created a Telegram bot and connected it to n8n. It now receives the file, processes it batch by batch and returns the corresponding answer to the user. The AI agent's memory needs to be improved, after which the bot will be ready.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>02/05/2026 14:18:49</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>Upgraded and improved the overall logic of the Telegram bot's AI n8n agentic workflow. It now handles the file better.</t>
         </is>
       </c>
     </row>
     <row r="99" ht="28.8" customHeight="1">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>04/05/2026 15:13:32</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>Created three web-based games for the Smart Wall screens, so that users can play while waiting for their package instead of being bored.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="28.8" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>05/05/2026 12:53:37</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>Created more games for the Smart Wall (web versions), and updated and fixed errors in the Merdzavan Telegram bot and the ONEX AI Agents self-improving agents.</t>
         </is>
       </c>
     </row>
     <row r="101" ht="43.2" customHeight="1">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>06/05/2026 14:56:30</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>Improved the "Catch the Parcels" Smart Wall game, made it full screen and removed all user touch elements. Updated and improved the AI Agents Score website according to the feedback received from the QC agents. Also updated and corrected the addresses of the corresponding communities in the agentic AI Telegram bot for Merdzavan.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="43.2" customHeight="1">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>07/05/2026 14:52:07</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>Created a new game, "ONEX Parcel Way", and updated all of the other games to be full screen and improved. Also fixed bugs and updated the memory of the Merdzavan Telegram AI agentic bot's AI agent (corrected the addresses and created JSON with the necessary structure, parsed from the CSV).</t>
         </is>
       </c>
     </row>
     <row r="103" ht="43.2" customHeight="1">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>08/05/2026 14:51:33</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>Made all of the Smart Wall games capture the username, tracking number, order number, and so on. Also deployed the fully working AI agent prompt improver AI workflow, which updates the prompt and creates a backup copy of the AI agent's prompt in the database (an n8n data table), in case the prompt is spoiled.</t>
         </is>
       </c>
     </row>
     <row r="104" ht="43.2" customHeight="1">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>11/05/2026 15:10:28</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>Upgraded the Smart Wall games. They now mock the user's QR scanning and start the game (the QR scan triggers the game to start): the user chooses a game and starts playing. Also received the materials needed to trigger the end of the game and started working on it.</t>
         </is>
       </c>
     </row>
     <row r="105" ht="28.8" customHeight="1">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>12/05/2026 14:50:52</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>Updated the Merdzavan Telegram AI bot agent's memory with the correct addresses and deployed it; waiting for feedback.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>13/05/2026 15:03:47</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>Updated the Telegram bot AI agent's prompt memory (corrected the addresses), and started data cleaning.</t>
         </is>
       </c>
     </row>
     <row r="107" ht="28.8" customHeight="1">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>14/05/2026 15:24:43</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>Updated the Smart Wall games. They now receive the "Your order is ready" trigger and end the game. Also updated and corrected the addresses in the AI agent's memory in the Merdzavan Telegram AI agentic bot's n8n workflow.</t>
         </is>
       </c>
     </row>
     <row r="108" ht="43.2" customHeight="1">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>15/05/2026 14:57:29</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>Met with the Head of Quality Control in order to receive the new requirements. Added a per-agent LEVEL 1 average score in Agent Details, made every criterion clickable for Edit Score (persisted to Supabase) and Give Feedback (which sends &lt;criterion description&gt; - &lt;feedback&gt; to n8n), and wired the default cluster weights to be fetched live from the webhook.</t>
         </is>
       </c>
     </row>
     <row r="109" ht="28.8" customHeight="1">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>18/05/2026 14:43:51</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>Updated the Merdzavan Telegram bot's addresses (the AI agent's memory) and deployed them. Also updated, validated and deployed all of the AI Agents Score agents' prompts, together with some UI and technical changes.</t>
         </is>
       </c>
     </row>
     <row r="110" ht="72" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>19/05/2026 15:00:27</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>Scraped and collected the necessary information about the ONEX support agents and the information that they should know. Cleaned it and brought it into a good state, ready to be given to the AI in the future.
 Also updated the n8n AI workflow, which now handles the "connection lost" and "customer closed the chat" cases with the AI agents, and the prompts work correctly.</t>
@@ -1807,60 +1810,60 @@
       </c>
     </row>
     <row r="111" ht="28.8" customHeight="1">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>20/05/2026 14:50:07</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B111" s="4" t="inlineStr">
         <is>
           <t>Cleaned, concatenated and added the necessary information to the analyst AI agent of the AI Agents Score project regarding the ONEX privacy policy and the correct procedures for placing orders (and more) with ONEX.</t>
         </is>
       </c>
     </row>
     <row r="112" ht="28.8" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>21/05/2026 14:55:01</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>Researched ways of implementing the "check 10 new tickets" step after feedback is given to the AI agent. It is now in the testing phase and has not been deployed yet.</t>
         </is>
       </c>
     </row>
     <row r="113" ht="28.8" customHeight="1">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>22/05/2026 14:52:44</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>Updated the AI agents score database and made a large number of UI updates. Deployed the new feature that shows the next 10 tickets after feedback is given, and made the UI user-friendly and easy to understand.</t>
         </is>
       </c>
     </row>
     <row r="114" ht="28.8" customHeight="1">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>23/05/2026 14:12:40</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>Updated some of the Merdzavan bot automation addresses, and deployed the Telegram bot's new memory with the corrected addresses.</t>
         </is>
       </c>
     </row>
     <row r="115" ht="100.8" customHeight="1">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>25/05/2026 15:17:06</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B115" s="4" t="inlineStr">
         <is>
           <t>Updated the "Send Another Feedback" window so that it displays the associated feedback criteria for each submitted feedback entry (for example, Feedback #1 – criterion name, Feedback #2 – criterion name).
 Added a "View Ticket Grades" button in the Next 10 Tickets section of Ticket Feedback.
@@ -1869,60 +1872,60 @@
       </c>
     </row>
     <row r="116" ht="43.2" customHeight="1">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>26/05/2026 15:07:04</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t>Added new functionality to the AI Agents Score website, so that when a user submits feedback, that exact ticket is updated with new validated grades and analysis, and the ticket is highlighted so that the user knows feedback has been given for it.</t>
         </is>
       </c>
     </row>
     <row r="117" ht="57.6" customHeight="1">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>27/05/2026 14:47:31</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>Updated the UI of the search bar in the "Tickets" section of the AI Agents Score website. Also updated the structure of the tickets in the website's backend (the Supabase PostgreSQL data table), added new columns and reflected them in the UI, so that users can distinguish the tickets that have received feedback from those that have not. All changes were deployed.</t>
         </is>
       </c>
     </row>
     <row r="118" ht="28.8" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>29/05/2026 14:56:08</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>Started splitting one AI agent into three (in fact four) AI agents, so that the work is done at higher quality and more simply, with faster and shorter prompts. Still in progress and being tested; not deployed yet.</t>
         </is>
       </c>
     </row>
     <row r="119" ht="28.8" customHeight="1">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>30/05/2026 14:31:16</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B119" s="4" t="inlineStr">
         <is>
           <t>Continued creating robust AI agents, separating the levels so that each level has its own AI agent, which means shorter prompts, lighter work and higher quality. Not finished and not deployed yet.</t>
         </is>
       </c>
     </row>
     <row r="120" ht="43.2" customHeight="1">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>01/06/2026 14:52:17</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>Continued working on the new separated level analyzer agents, made a large number of updates and improvements, and deployed them.
 Also started working on updating and adding ONEX user levels.</t>
@@ -1930,12 +1933,12 @@
       </c>
     </row>
     <row r="121" ht="43.2" customHeight="1">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>02/06/2026 15:28:52</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>Updated the self-improving AI agentic n8n workflow and ran several tests; the level 1 analyst update is done, and levels 2 and 3 are left.
 Also carried out research and tests on searching for and updating ONEX user levels (the new update).</t>
@@ -1943,36 +1946,36 @@
       </c>
     </row>
     <row r="122" ht="28.8" customHeight="1">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>03/06/2026 14:57:32</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B122" s="4" t="inlineStr">
         <is>
           <t>Updated and almost finished the self-improving AI agentic workflow of the AI Agents Score project; it still needs some tests and deployment.</t>
         </is>
       </c>
     </row>
     <row r="123" ht="28.8" customHeight="1">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>04/06/2026 14:41:37</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>Updated the self-improving AI agentic workflow, tested and validated it, made it robust and deployed it, and it is now ready for real-life tests.</t>
         </is>
       </c>
     </row>
     <row r="124" ht="57.6" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t>05/06/2026 14:59:28</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>Added, tested, validated and deployed the latest UI, backend and logic updates of the new self-improving AI workflow.
 Also started working on clustering tickets by topic, as a continuation of the self-improving agents and the tracking of their quality.</t>
@@ -1980,72 +1983,72 @@
       </c>
     </row>
     <row r="125" ht="72" customHeight="1">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t>06/06/2026 14:51:10</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>Added a per-ticket topic to the AI Agents Score system — shown as a dedicated column and detail box on the Tickets page — by plumbing a new topic database column through the tickets snapshot edge function and the ticket parser. Also reworked the post-feedback "Feedback Watch" so that it clusters by topic instead of by agent: after any correction it tracks the next 10 tickets on the same topic that are graded afterwards, which makes it possible to verify whether the AI learned the correction and applied it to similar tickets.</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>08/06/2026 14:46:01</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B126" s="4" t="inlineStr">
         <is>
           <t>Corrected the topic setter AI agent's prompt, added one topic and deployed the change.</t>
         </is>
       </c>
     </row>
     <row r="127" ht="28.8" customHeight="1">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t>09/06/2026 14:55:08</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="B127" s="4" t="inlineStr">
         <is>
           <t>Ran tests and traced the new AI agentic n8n workflow for analyzing and grading tickets (customer support workers).</t>
         </is>
       </c>
     </row>
     <row r="128" ht="28.8" customHeight="1">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="A128" s="3" t="inlineStr">
         <is>
           <t>10/06/2026 14:39:26</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B128" s="4" t="inlineStr">
         <is>
           <t>Moved the QA automation from dev/staging to live. Fixed the live verification bug and the WSL virtual environment setup failure, and made the WSL and Windows toolchains coexist cleanly.</t>
         </is>
       </c>
     </row>
     <row r="129" ht="28.8" customHeight="1">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="A129" s="3" t="inlineStr">
         <is>
           <t>11/06/2026 14:42:54</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B129" s="4" t="inlineStr">
         <is>
           <t>Held a meeting with the QA team's team lead and received new tasks. Also showcased the new automation flow and received positive feedback, and started working on the QA's new (additional) flow.</t>
         </is>
       </c>
     </row>
     <row r="130" ht="72" customHeight="1">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t>12/06/2026 14:39:57</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>Officially started development of the ONEX Academy project. The goal is to build an engaging, quiz-based web app that support agents can use to test their knowledge.
 Also continued updating, testing and deploying the QA automation project for user and parcel creation, box creation and addition, and so on; some cases still need to be reviewed and corrected.</t>
@@ -2053,12 +2056,12 @@
       </c>
     </row>
     <row r="131" ht="43.2" customHeight="1">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t>13/06/2026 14:39:45</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>Updated the live QA automation flow, deployed it on the QA team lead's PC and tested it.
 Also held a meeting with the quality control team, received tasks and showed them the prototype of the project.</t>
@@ -2066,36 +2069,36 @@
       </c>
     </row>
     <row r="132" ht="28.8" customHeight="1">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t>15/06/2026 15:03:33</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="B132" s="4" t="inlineStr">
         <is>
           <t>Created, tested and deployed a task scheduler that sends all new images to the Amazon AWS S3 server and stores them with working URLs.</t>
         </is>
       </c>
     </row>
     <row r="133" ht="57.6" customHeight="1">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t>16/06/2026 12:13:29</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr">
+      <c r="B133" s="4" t="inlineStr">
         <is>
           <t>Built 11 new academy features (media questions, timers, topics, multi-correct answers, levels, link/roadmap, explanations, timing analytics and screenshot deterrence) and removed the flashcards. After the schema was accidentally applied to the live "Agents Tickets" database (since restored), set up a dedicated Supabase project (imzedtezqkqrynjzvcxq) and pointed the app at it. Left to do: publish in Lovable and add the onex@onex.am admin.</t>
         </is>
       </c>
     </row>
     <row r="134" ht="57.6" customHeight="1">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t>17/06/2026 15:00:41</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t>Synced the database schema, types and RPCs, and fixed scoring, authentication and gameplay bugs. The SQL has been run; the only remaining step is to create the quiz media storage bucket.
 Also ran tests, made updates and improvements, fixed bugs and deployed.</t>
@@ -2103,12 +2106,12 @@
       </c>
     </row>
     <row r="135" ht="43.2" customHeight="1">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t>18/06/2026 14:27:06</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
+      <c r="B135" s="4" t="inlineStr">
         <is>
           <t>Received feedback on ONEX Academy.
 Also ran tests and received a new task for the Amazon S3 bucket import automation, so that the images have URLs.</t>
@@ -2116,72 +2119,72 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t>19/06/2026 14:40:49</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B136" s="4" t="inlineStr">
         <is>
           <t>Ran tests and improvements and deployed the automatic image uploader for the Amazon S3 bucket.</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>20/06/2026 14:10:37</t>
         </is>
       </c>
-      <c r="B137" s="3" t="inlineStr">
+      <c r="B137" s="4" t="inlineStr">
         <is>
           <t>Ran tests and improvements and deployed the automatic image uploader for the Amazon S3 bucket.</t>
         </is>
       </c>
     </row>
     <row r="138" ht="28.8" customHeight="1">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="A138" s="3" t="inlineStr">
         <is>
           <t>22/06/2026 14:24:08</t>
         </is>
       </c>
-      <c r="B138" s="3" t="inlineStr">
+      <c r="B138" s="4" t="inlineStr">
         <is>
           <t>Built a weekly timesheet in Google Sheets with five-minute time dropdowns (from 07:00 onwards) for the start and end times, which automatically calculate and sum each person's worked hours in the SUMMARY column.</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="A139" s="3" t="inlineStr">
         <is>
           <t>23/06/2026 14:27:00</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B139" s="4" t="inlineStr">
         <is>
           <t>Fixed the time setting issue with the Google Sheets dropdown button, and made it robust and flexible.</t>
         </is>
       </c>
     </row>
     <row r="140" ht="28.8" customHeight="1">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t>24/06/2026 14:27:00</t>
         </is>
       </c>
-      <c r="B140" s="3" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>Created and deployed the Amazon S3 bucket import automation on another PC, so that the images have URLs; the only remaining steps are to set the Amazon credentials via the terminal and to perform the same task on one more PC.</t>
         </is>
       </c>
     </row>
     <row r="141" ht="57.6" customHeight="1">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t>25/06/2026 13:52:18</t>
         </is>
       </c>
-      <c r="B141" s="3" t="inlineStr">
+      <c r="B141" s="4" t="inlineStr">
         <is>
           <t>Added AI free-text grading using the Gemini 3 Flash model.
 Enabled custom question points and resolved the image upload issue.
@@ -2190,24 +2193,24 @@
       </c>
     </row>
     <row r="142" ht="28.8" customHeight="1">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>26/06/2026 14:25:13</t>
         </is>
       </c>
-      <c r="B142" s="3" t="inlineStr">
+      <c r="B142" s="4" t="inlineStr">
         <is>
           <t>Fixed the issue where free-text quiz questions did not show an answer input field. Consolidated everything into a single Supabase project and applied the database migration. Also fixed the loading of the dev environment, which enabled AI grading to work correctly.</t>
         </is>
       </c>
     </row>
     <row r="143" ht="72" customHeight="1">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>27/06/2026 14:39:35</t>
         </is>
       </c>
-      <c r="B143" s="3" t="inlineStr">
+      <c r="B143" s="4" t="inlineStr">
         <is>
           <t>Updated the last ONEX China computer, so all parcels with a tracking code in China are now automatically uploaded to the Amazon S3 bucket database and receive URLs.
 Also held a meeting with the chief head of quality control, received new tasks and feedback about the AI-powered ONEX Academy quiz website, and made major updates to it, tested them and deployed.</t>
@@ -2215,12 +2218,12 @@
       </c>
     </row>
     <row r="144" ht="57.6" customHeight="1">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="A144" s="3" t="inlineStr">
         <is>
           <t>29/06/2026 15:03:18</t>
         </is>
       </c>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t>Added two new features to the ONEX Academy project:
 1. Added a skip feature, so that users can skip a question and see its correct answer.
@@ -2229,12 +2232,12 @@
       </c>
     </row>
     <row r="145" ht="158.4" customHeight="1">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="A145" s="3" t="inlineStr">
         <is>
           <t>30/06/2026 14:41:10</t>
         </is>
       </c>
-      <c r="B145" s="3" t="inlineStr">
+      <c r="B145" s="4" t="inlineStr">
         <is>
           <t>Worked on adding the ONEX.am watermark to the images in the Amazon S3 bucket auto-uploading process; it still needs further tests, updates and deployment.
 Also added four new features to the ONEX Academy project:
@@ -2245,36 +2248,36 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="A146" s="3" t="inlineStr">
         <is>
           <t>02/07/2026 14:35:35</t>
         </is>
       </c>
-      <c r="B146" s="3" t="inlineStr">
+      <c r="B146" s="4" t="inlineStr">
         <is>
           <t>Tested and validated the ONEX Academy website in order to make sure that it is safely deployed.</t>
         </is>
       </c>
     </row>
     <row r="147" ht="28.8" customHeight="1">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="A147" s="3" t="inlineStr">
         <is>
           <t>03/07/2026 13:49:11</t>
         </is>
       </c>
-      <c r="B147" s="3" t="inlineStr">
+      <c r="B147" s="4" t="inlineStr">
         <is>
           <t>Started deploying the Amazon S3 bucket upload automation project, which includes image quality reduction and watermark adding (Python needs to be installed on the ONEX China computers in order for the code to work).</t>
         </is>
       </c>
     </row>
     <row r="148" ht="43.2" customHeight="1">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="A148" s="3" t="inlineStr">
         <is>
           <t>04/07/2026 14:14:53</t>
         </is>
       </c>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="B148" s="4" t="inlineStr">
         <is>
           <t>Continued working on the Amazon S3 bucket auto-uploading on the ONEX China computers.
 Also started working on the article maker n8n AI agentic workflow for footdraw.com.</t>
@@ -2282,24 +2285,24 @@
       </c>
     </row>
     <row r="149" ht="28.8" customHeight="1">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="A149" s="3" t="inlineStr">
         <is>
           <t>06/07/2026 15:01:59</t>
         </is>
       </c>
-      <c r="B149" s="3" t="inlineStr">
+      <c r="B149" s="4" t="inlineStr">
         <is>
           <t>Successfully built an automated n8n workflow for FootDraw articles. It generates structured Markdown content, SEO metadata and custom images.</t>
         </is>
       </c>
     </row>
     <row r="150" ht="57.6" customHeight="1">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="A150" s="3" t="inlineStr">
         <is>
           <t>07/07/2026 15:54:50</t>
         </is>
       </c>
-      <c r="B150" s="3" t="inlineStr">
+      <c r="B150" s="4" t="inlineStr">
         <is>
           <t>Held a meeting about the general use of AI across the ONEX.am team.
 Also tested, validated, improved and finished the AI article maker n8n agentic workflow, and started creating the AI translation agentic workflows.</t>
@@ -2307,12 +2310,12 @@
       </c>
     </row>
     <row r="151" ht="115.2" customHeight="1">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="A151" s="3" t="inlineStr">
         <is>
           <t>08/07/2026 16:02:22</t>
         </is>
       </c>
-      <c r="B151" s="3" t="inlineStr">
+      <c r="B151" s="4" t="inlineStr">
         <is>
           <t>Built an n8n workflow that translates JSON using Gemini; the code parses the AI outputs, restores the images and maps the languages.
 Also carried out a task review and received new tasks and feedback for the ONEX Academy website.
@@ -2321,12 +2324,12 @@
       </c>
     </row>
     <row r="152" ht="86.40000000000001" customHeight="1">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="A152" s="3" t="inlineStr">
         <is>
           <t>09/07/2026 15:01:22</t>
         </is>
       </c>
-      <c r="B152" s="3" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>Updated the card game number setting input field on the ONEX Academy website, added a dynamic enlarging feature for text input fields, and added a UI text editing field to the website.
 Also finished the article translator workflow's AI agent prompts, code nodes and output parsers; the whole workflow has now been tested, validated and deployed, and it translates correctly into 7 different languages and returns the webhook response correctly.</t>
@@ -2334,36 +2337,36 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="A153" s="3" t="inlineStr">
         <is>
           <t>10/07/2026 15:01:22</t>
         </is>
       </c>
-      <c r="B153" s="3" t="inlineStr">
+      <c r="B153" s="4" t="inlineStr">
         <is>
           <t>Held a meeting with the CTO, clarified and organized the tasks, presented them, and continued with the tasks for the day.</t>
         </is>
       </c>
     </row>
     <row r="154" ht="43.2" customHeight="1">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="A154" s="3" t="inlineStr">
         <is>
           <t>13/07/2026 15:03:25</t>
         </is>
       </c>
-      <c r="B154" s="3" t="inlineStr">
+      <c r="B154" s="4" t="inlineStr">
         <is>
           <t>Fixed the AI test summary, which was silently failing with no diagnosable cause, by correcting the error logging, adding clip-tolerant validation and making the model configuration reliable.</t>
         </is>
       </c>
     </row>
     <row r="155" ht="43.2" customHeight="1">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="A155" s="3" t="inlineStr">
         <is>
           <t>14/07/2026 14:43:55</t>
         </is>
       </c>
-      <c r="B155" s="3" t="inlineStr">
+      <c r="B155" s="4" t="inlineStr">
         <is>
           <t>Enabled Telegram-based registration for ONEX Academy on its Lovable deployment.
 Configured the bot, the migration and the webhook, then fixed and verified the signup.</t>
@@ -2371,12 +2374,12 @@
       </c>
     </row>
     <row r="156" ht="43.2" customHeight="1">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="A156" s="3" t="inlineStr">
         <is>
           <t>15/07/2026 15:02:50</t>
         </is>
       </c>
-      <c r="B156" s="3" t="inlineStr">
+      <c r="B156" s="4" t="inlineStr">
         <is>
           <t>Added new features to ONEX Academy:
 1. New badges with their own icons and pictures.
@@ -2385,12 +2388,12 @@
       </c>
     </row>
     <row r="157" ht="43.2" customHeight="1">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="A157" s="3" t="inlineStr">
         <is>
           <t>16/07/2026 14:52:21</t>
         </is>
       </c>
-      <c r="B157" s="3" t="inlineStr">
+      <c r="B157" s="4" t="inlineStr">
         <is>
           <t>Tested, validated and deployed the new badges and level animation feature.
 Also added new UI updates to the ONEX Academy website project.</t>
@@ -2398,48 +2401,48 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="A158" s="3" t="inlineStr">
         <is>
           <t>17/07/2026 14:52:21</t>
         </is>
       </c>
-      <c r="B158" s="3" t="inlineStr">
+      <c r="B158" s="4" t="inlineStr">
         <is>
           <t>Started working on the mobile version of the ONEX Academy project website.</t>
         </is>
       </c>
     </row>
     <row r="159" ht="43.2" customHeight="1">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="A159" s="3" t="inlineStr">
         <is>
           <t>18/07/2026 13:38:28</t>
         </is>
       </c>
-      <c r="B159" s="3" t="inlineStr">
+      <c r="B159" s="4" t="inlineStr">
         <is>
           <t>Added a dedicated mobile version mode without changing the desktop layout. Built a three-dots hamburger menu grouping play, leaderboard and settings. Added a mobile text size adjuster to enlarge quizzes and inputs. Improved the memory card game with a red wrong-pair animation and click-flip fixes.</t>
         </is>
       </c>
     </row>
     <row r="160" ht="28.8" customHeight="1">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="A160" s="3" t="inlineStr">
         <is>
           <t>20/07/2026 12:53:36</t>
         </is>
       </c>
-      <c r="B160" s="3" t="inlineStr">
+      <c r="B160" s="4" t="inlineStr">
         <is>
           <t>Updated and improved the website's features, making it nicer and more user-friendly, worked on testing and finding bugs, corrected and fixed them and deployed the changes, and also worked on improvements to the website's mobile version.</t>
         </is>
       </c>
     </row>
     <row r="161" ht="72" customHeight="1">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="A161" s="3" t="inlineStr">
         <is>
           <t>22/07/2026 14:23:15</t>
         </is>
       </c>
-      <c r="B161" s="3" t="inlineStr">
+      <c r="B161" s="4" t="inlineStr">
         <is>
           <t>Built a new "Questions Database" quiz type that serves random question subsets with per-week play limits. Added admin controls for the pool size, limits, topic balancing and per-player resets.
 Also added an admin button that copies quiz questions into any Questions Database, and merged Lovable's security fixes with the feature and pushed them to main.</t>
@@ -2447,48 +2450,48 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="A162" s="3" t="inlineStr">
         <is>
           <t>23/07/2026 14:43:17</t>
         </is>
       </c>
-      <c r="B162" s="3" t="inlineStr">
+      <c r="B162" s="4" t="inlineStr">
         <is>
           <t>Researched Armenian speech-to-text models for use in the AI Agents Score quality control project.</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="A163" s="3" t="inlineStr">
         <is>
           <t>24/07/2026 15:05:27</t>
         </is>
       </c>
-      <c r="B163" s="3" t="inlineStr">
+      <c r="B163" s="4" t="inlineStr">
         <is>
           <t>Continued researching Armenian speech-to-text models for use in the AI Agents Score quality control project.</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="A164" s="3" t="inlineStr">
         <is>
           <t>25/07/2026 14:24:08</t>
         </is>
       </c>
-      <c r="B164" s="3" t="inlineStr">
+      <c r="B164" s="4" t="inlineStr">
         <is>
           <t>Continued researching Armenian speech-to-text models for use in the AI Agents Score quality control project.</t>
         </is>
       </c>
     </row>
     <row r="165" ht="72" customHeight="1">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="A165" s="3" t="inlineStr">
         <is>
           <t>27/07/2026 14:26:47</t>
         </is>
       </c>
-      <c r="B165" s="3" t="inlineStr">
+      <c r="B165" s="4" t="inlineStr">
         <is>
           <t>Investigated, located and fixed the problem in the AI agentic translator n8n workflow for footdraw.com, then updated and deployed it; it no longer returns a 500 error.
 Also updated the AI agentic article maker n8n workflow for footdraw.com, which now generates images without English (or any other language) text on them.</t>
@@ -2496,24 +2499,24 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="A166" s="3" t="inlineStr">
         <is>
           <t>28/07/2026 12:52:31</t>
         </is>
       </c>
-      <c r="B166" s="3" t="inlineStr">
+      <c r="B166" s="4" t="inlineStr">
         <is>
           <t>Continued researching Armenian speech-to-text models for use in the AI Agents Score quality control project.</t>
         </is>
       </c>
     </row>
     <row r="167" ht="43.2" customHeight="1">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="A167" s="3" t="inlineStr">
         <is>
           <t>29/07/2026 14:32:43</t>
         </is>
       </c>
-      <c r="B167" s="3" t="inlineStr">
+      <c r="B167" s="4" t="inlineStr">
         <is>
           <t>Researched Armenian speech-to-text models for use in the AI Agents Score quality control project.
 Found several models to test with, created a neat UI for browsing the ONEX call MP3 files and the models, and tested it locally.</t>
@@ -2521,24 +2524,24 @@
       </c>
     </row>
     <row r="168" ht="43.2" customHeight="1">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="A168" s="3" t="inlineStr">
         <is>
           <t>30/07/2026 14:32:43</t>
         </is>
       </c>
-      <c r="B168" s="3" t="inlineStr">
+      <c r="B168" s="4" t="inlineStr">
         <is>
           <t>Replaced the Telegram deep-link signup in ONEX Academy with a hashed six-digit confirmation code. Added a confirm-password field that shows a live tick or cross icon. The code has been shipped to main; the remaining blocker is the unapplied live migration.</t>
         </is>
       </c>
     </row>
     <row r="169" ht="43.2" customHeight="1">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="A169" s="3" t="inlineStr">
         <is>
           <t>31/07/2026 13:52:50</t>
         </is>
       </c>
-      <c r="B169" s="3" t="inlineStr">
+      <c r="B169" s="4" t="inlineStr">
         <is>
           <t>Replaced the dead bot, removed the email verification and registered the webhook.
 Added weekly play limits for every quiz, greying out the exhausted cards.
@@ -2547,12 +2550,12 @@
       </c>
     </row>
     <row r="170" ht="72" customHeight="1">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="A170" s="3" t="inlineStr">
         <is>
           <t>03/08/2026 15:26:53</t>
         </is>
       </c>
-      <c r="B170" s="3" t="inlineStr">
+      <c r="B170" s="4" t="inlineStr">
         <is>
           <t>Swapped in the new @AcademyONEXbot and registered its verification webhook.
 Fixed the six-digit signup codes and the authentication, database and media bucket security gaps.
@@ -2561,12 +2564,12 @@
       </c>
     </row>
     <row r="171" ht="57.6" customHeight="1">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="A171" s="3" t="inlineStr">
         <is>
           <t>04/08/2026 14:53:15</t>
         </is>
       </c>
-      <c r="B171" s="3" t="inlineStr">
+      <c r="B171" s="4" t="inlineStr">
         <is>
           <t>Replaced the Telegram bot; the verification and webhook now work.
 Added an admin panel for sending Telegram reminders.
@@ -2576,48 +2579,48 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="A172" s="3" t="inlineStr">
         <is>
           <t>05/08/2026 15:05:37</t>
         </is>
       </c>
-      <c r="B172" s="3" t="inlineStr">
+      <c r="B172" s="4" t="inlineStr">
         <is>
           <t>Continued researching Armenian speech-to-text models for use in the AI Agents Score quality control project.</t>
         </is>
       </c>
     </row>
     <row r="173" ht="28.8" customHeight="1">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="A173" s="3" t="inlineStr">
         <is>
           <t>06/08/2026 16:03:12</t>
         </is>
       </c>
-      <c r="B173" s="3" t="inlineStr">
+      <c r="B173" s="4" t="inlineStr">
         <is>
           <t>Started creating the AI ONEX blog maker workflow together with its web version, so that it can be deployed on the main ONEX website in the future.</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="A174" s="3" t="inlineStr">
         <is>
           <t>07/08/2026 14:57:22</t>
         </is>
       </c>
-      <c r="B174" s="3" t="inlineStr">
+      <c r="B174" s="4" t="inlineStr">
         <is>
           <t>Continued creating the ONEX.am blog making AI workflow.</t>
         </is>
       </c>
     </row>
     <row r="175" ht="72" customHeight="1">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="A175" s="3" t="inlineStr">
         <is>
           <t>10/08/2026 15:53:09</t>
         </is>
       </c>
-      <c r="B175" s="3" t="inlineStr">
+      <c r="B175" s="4" t="inlineStr">
         <is>
           <t>Confirmed that Tilda has no write API, and chose self-hosted rendering instead.
 Built image offloading, slug publishing, SSR public pages and the Tilda hub.
@@ -2629,12 +2632,12 @@
       </c>
     </row>
     <row r="176" ht="72" customHeight="1">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="A176" s="3" t="inlineStr">
         <is>
           <t>11/08/2026 15:59:35</t>
         </is>
       </c>
-      <c r="B176" s="3" t="inlineStr">
+      <c r="B176" s="4" t="inlineStr">
         <is>
           <t>Confirmed that Tilda has no write API, and built three export routes instead.
 Shipped image offloading, publishing, SSR pages, the hub block and HTML export.
@@ -2643,60 +2646,60 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="A177" s="3" t="inlineStr">
         <is>
           <t>12/08/2026 16:00:00</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B177" s="4" t="inlineStr">
         <is>
           <t>Updated the automation of the ONEX AI blog auto-maker and demonstrated it to the corresponding specialist.</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="A178" s="3" t="inlineStr">
         <is>
           <t>13/08/2026 15:11:54</t>
         </is>
       </c>
-      <c r="B178" s="3" t="inlineStr">
+      <c r="B178" s="4" t="inlineStr">
         <is>
           <t>Researched Armenian speech-to-text models for use in the AI Agents Score quality control project.</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="A179" s="3" t="inlineStr">
         <is>
           <t>14/08/2026 15:57:18</t>
         </is>
       </c>
-      <c r="B179" s="3" t="inlineStr">
+      <c r="B179" s="4" t="inlineStr">
         <is>
           <t>Researched Armenian speech-to-text models for use in the AI Agents Score quality control project.</t>
         </is>
       </c>
     </row>
     <row r="180" ht="43.2" customHeight="1">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="A180" s="3" t="inlineStr">
         <is>
           <t>17/08/2026 15:58:01</t>
         </is>
       </c>
-      <c r="B180" s="3" t="inlineStr">
+      <c r="B180" s="4" t="inlineStr">
         <is>
           <t>Met with the quality control heads and received fifteen tasks. These necessary changes will be completed by early next week, and once they are ready I will notify you for another testing session.</t>
         </is>
       </c>
     </row>
     <row r="181" ht="409.6" customHeight="1">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="A181" s="3" t="inlineStr">
         <is>
           <t>18/08/2026 15:39:23</t>
         </is>
       </c>
-      <c r="B181" s="3" t="inlineStr">
+      <c r="B181" s="4" t="inlineStr">
         <is>
           <t>Badges
 Added badges that admins can award by hand, with a picture and text.
@@ -2728,12 +2731,12 @@
       </c>
     </row>
     <row r="182" ht="403.2" customHeight="1">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="A182" s="3" t="inlineStr">
         <is>
           <t>19/08/2026 15:21:00</t>
         </is>
       </c>
-      <c r="B182" s="3" t="inlineStr">
+      <c r="B182" s="4" t="inlineStr">
         <is>
           <t>1. Answers with text, link and picture
 Admins can now choose, per question, how the player answers: free text, link, picture, or any combination. Each ticked box gets its own "correct answer" field, and the AI compares every part that the player submits — including looking at their screenshot — into a single score.
@@ -2752,12 +2755,12 @@
       </c>
     </row>
     <row r="183" ht="57.6" customHeight="1">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="A183" s="3" t="inlineStr">
         <is>
           <t>21/08/2026 15:24:29</t>
         </is>
       </c>
-      <c r="B183" s="3" t="inlineStr">
+      <c r="B183" s="4" t="inlineStr">
         <is>
           <t>[ONEX Academy]
 Added a picture zoom feature to the questions, so that users can view them full screen, with a zoom button (including + and - buttons) to zoom in on a picture and read the text or handwritten content.
@@ -2772,12 +2775,12 @@
       </c>
     </row>
     <row r="184" ht="244.8" customHeight="1">
-      <c r="A184" s="2" t="inlineStr">
+      <c r="A184" s="3" t="inlineStr">
         <is>
           <t>24/08/2026 15:57:23</t>
         </is>
       </c>
-      <c r="B184" s="3" t="inlineStr">
+      <c r="B184" s="4" t="inlineStr">
         <is>
           <t>In the AI Agents Score project:
 Added a multi-criteria feedback display, editable ticket levels and per-criterion justification copy buttons.
@@ -2788,36 +2791,36 @@
       </c>
     </row>
     <row r="185" ht="72" customHeight="1">
-      <c r="A185" s="2" t="inlineStr">
+      <c r="A185" s="3" t="inlineStr">
         <is>
           <t>25/08/2026 16:05:00</t>
         </is>
       </c>
-      <c r="B185" s="3" t="inlineStr">
+      <c r="B185" s="4" t="inlineStr">
         <is>
           <t>Created a new AI agentic workflow in n8n that retrieves new Gmail messages, parses them and extracts the tracking codes and order numbers (IDs), and collects everything into a dedicated Google Sheet together with the sender's email, the date and time, the sender, the recipient, the order ID, the tracking code, and so on. All of this information is stored, and the workflow is triggered every minute in order to update the Google Sheets list.</t>
         </is>
       </c>
     </row>
     <row r="186" ht="57.6" customHeight="1">
-      <c r="A186" s="2" t="inlineStr">
+      <c r="A186" s="3" t="inlineStr">
         <is>
           <t>26/08/2026 14:57:29</t>
         </is>
       </c>
-      <c r="B186" s="3" t="inlineStr">
+      <c r="B186" s="4" t="inlineStr">
         <is>
           <t>Updated the AI agentic n8n workflow for the automation of ONEX's Buy For Me service in Gmail, regarding the tracking code and the order ID/number.</t>
         </is>
       </c>
     </row>
     <row r="187" ht="28.8" customHeight="1">
-      <c r="A187" s="2" t="inlineStr">
+      <c r="A187" s="3" t="inlineStr">
         <is>
           <t>27/08/2026 15:45:55</t>
         </is>
       </c>
-      <c r="B187" s="3" t="inlineStr">
+      <c r="B187" s="4" t="inlineStr">
         <is>
           <t>Added a node that marks processed Gmail messages as unread.
 Fixed the expressions so that they extract the exact courier and title.
@@ -2826,12 +2829,12 @@
       </c>
     </row>
     <row r="188" ht="43.2" customHeight="1">
-      <c r="A188" s="2" t="inlineStr">
+      <c r="A188" s="3" t="inlineStr">
         <is>
           <t>28/08/2026 15:41:14</t>
         </is>
       </c>
-      <c r="B188" s="3" t="inlineStr">
+      <c r="B188" s="4" t="inlineStr">
         <is>
           <t>[Buy For Me]
 • Created a Telegram bot notification for every updated or added row.
@@ -2841,12 +2844,12 @@
       </c>
     </row>
     <row r="189" ht="86.40000000000001" customHeight="1">
-      <c r="A189" s="2" t="inlineStr">
+      <c r="A189" s="3" t="inlineStr">
         <is>
           <t>31/08/2026 14:18:52</t>
         </is>
       </c>
-      <c r="B189" s="3" t="inlineStr">
+      <c r="B189" s="4" t="inlineStr">
         <is>
           <t>[Logistics]
 • Merged the 141 XML files correctly, sent them to the logistics chief and obtained approval that the files are correct.
@@ -2856,12 +2859,12 @@
       </c>
     </row>
     <row r="190" ht="72" customHeight="1">
-      <c r="A190" s="2" t="inlineStr">
+      <c r="A190" s="3" t="inlineStr">
         <is>
           <t>01/09/2026 19:41:58</t>
         </is>
       </c>
-      <c r="B190" s="3" t="inlineStr">
+      <c r="B190" s="4" t="inlineStr">
         <is>
           <t>[Buy For Me]
 • Removed the «ԳՆԷՆՑՐ ԻՄ ՓՈԽԱՐԵՆ» նոր պատվերի հարցում request, so that it is no longer taken into account.
@@ -2874,12 +2877,12 @@
       </c>
     </row>
     <row r="191" ht="129.6" customHeight="1">
-      <c r="A191" s="2" t="inlineStr">
+      <c r="A191" s="3" t="inlineStr">
         <is>
           <t>02/09/2026 19:32:50</t>
         </is>
       </c>
-      <c r="B191" s="3" t="inlineStr">
+      <c r="B191" s="4" t="inlineStr">
         <is>
           <t>[Buy For Me]
 • Added Rob's new email and made it tracked, with Telegram bot alerts for it as well.</t>
@@ -2887,12 +2890,12 @@
       </c>
     </row>
     <row r="192" ht="28.8" customHeight="1">
-      <c r="A192" s="2" t="inlineStr">
+      <c r="A192" s="3" t="inlineStr">
         <is>
           <t>03/09/2026 19:50:18</t>
         </is>
       </c>
-      <c r="B192" s="3" t="inlineStr">
+      <c r="B192" s="4" t="inlineStr">
         <is>
           <t>[Buy For Me]
 • Deleted the email row from the Telegram bot message.
@@ -2903,12 +2906,12 @@
       </c>
     </row>
     <row r="193" ht="43.2" customHeight="1">
-      <c r="A193" s="2" t="inlineStr">
+      <c r="A193" s="3" t="inlineStr">
         <is>
           <t>04/09/2026 18:06:19</t>
         </is>
       </c>
-      <c r="B193" s="3" t="inlineStr">
+      <c r="B193" s="4" t="inlineStr">
         <is>
           <t>[Buy For Me]
 • Continued working on the automated button clicking system.
@@ -2919,10 +2922,10 @@
       </c>
     </row>
     <row r="194" ht="28.8" customHeight="1">
-      <c r="A194" s="4" t="n">
+      <c r="A194" s="5" t="n">
         <v>46272.79972222223</v>
       </c>
-      <c r="B194" s="3" t="inlineStr">
+      <c r="B194" s="4" t="inlineStr">
         <is>
           <t>[Buy For Me]
 • changed the links of the telegram bot "BFM request link" to the real searched request links with oder id already searching
@@ -2934,12 +2937,12 @@
       </c>
     </row>
     <row r="195" ht="86.40000000000001" customHeight="1">
-      <c r="A195" s="4" t="inlineStr">
+      <c r="A195" s="5" t="inlineStr">
         <is>
           <t>08/09/2026 20:14:36</t>
         </is>
       </c>
-      <c r="B195" s="3" t="inlineStr">
+      <c r="B195" s="4" t="inlineStr">
         <is>
           <t>[Buy For Me]
 • only tracking id's messages bot will send
@@ -2955,12 +2958,12 @@
       </c>
     </row>
     <row r="196" ht="100.8" customHeight="1">
-      <c r="A196" s="2" t="inlineStr">
+      <c r="A196" s="3" t="inlineStr">
         <is>
           <t>09/09/2026 20:00:35</t>
         </is>
       </c>
-      <c r="B196" s="3" t="inlineStr">
+      <c r="B196" s="4" t="inlineStr">
         <is>
           <t>[Buy For Me]
 • smoke tested all, everything works perfect, telegram bot sends message only when the tracking code is detected (and the specific name detected)
@@ -2970,12 +2973,12 @@
       </c>
     </row>
     <row r="197" ht="86.40000000000001" customHeight="1">
-      <c r="A197" s="2" t="inlineStr">
+      <c r="A197" s="3" t="inlineStr">
         <is>
           <t>10/09/2026 18:51:07</t>
         </is>
       </c>
-      <c r="B197" s="3" t="inlineStr">
+      <c r="B197" s="4" t="inlineStr">
         <is>
           <t>[Logistics]
 • test the bug-fixed version of the trade.gov.am automation
@@ -2986,12 +2989,12 @@
       </c>
     </row>
     <row r="198" ht="158.4" customHeight="1">
-      <c r="A198" s="2" t="inlineStr">
+      <c r="A198" s="3" t="inlineStr">
         <is>
           <t>11/09/2026 20:03:42</t>
         </is>
       </c>
-      <c r="B198" s="3" t="inlineStr">
+      <c r="B198" s="4" t="inlineStr">
         <is>
           <t>[Logistics]
 • 1196 number check to make all the pages data points appear in the exel
@@ -3005,12 +3008,12 @@
       </c>
     </row>
     <row r="199" ht="57.6" customHeight="1">
-      <c r="A199" s="2" t="inlineStr">
+      <c r="A199" s="3" t="inlineStr">
         <is>
           <t>14/09/2026 19:05:17</t>
         </is>
       </c>
-      <c r="B199" s="3" t="inlineStr">
+      <c r="B199" s="4" t="inlineStr">
         <is>
           <t>[Buy For Me]
 • Changed supported countries to only am, de, gr, it, pl, es, ae, uk, and us; removed obsolete country markets; improved product-link parsing for Zara, H&amp;M, Puma, U.S. Polo, and Carpisa; added support for uspashop.com; expanded link validation tests; updated documentation and examples; committed and pushed all changes to main.</t>
@@ -3018,12 +3021,12 @@
       </c>
     </row>
     <row r="200" ht="187.2" customHeight="1">
-      <c r="A200" s="2" t="inlineStr">
+      <c r="A200" s="3" t="inlineStr">
         <is>
           <t>17/09/2026 15:22:21</t>
         </is>
       </c>
-      <c r="B200" s="3" t="inlineStr">
+      <c r="B200" s="4" t="inlineStr">
         <is>
           <t>[DealFinder]
 • made these updates:
@@ -3041,12 +3044,12 @@
       </c>
     </row>
     <row r="201" ht="72" customHeight="1">
-      <c r="A201" s="2" t="inlineStr">
+      <c r="A201" s="3" t="inlineStr">
         <is>
           <t>23/09/2026 19:56:19</t>
         </is>
       </c>
-      <c r="B201" s="3" t="inlineStr">
+      <c r="B201" s="4" t="inlineStr">
         <is>
           <t>[ONEX-Academy]
 • fix the plane animation bugs (delays that are shown in the next page)
@@ -3056,12 +3059,12 @@
       </c>
     </row>
     <row r="202" ht="28.8" customHeight="1">
-      <c r="A202" s="2" t="inlineStr">
+      <c r="A202" s="3" t="inlineStr">
         <is>
           <t>18/09/2026 19:56:06</t>
         </is>
       </c>
-      <c r="B202" s="3" t="inlineStr">
+      <c r="B202" s="4" t="inlineStr">
         <is>
           <t>[ONEX-Academy]
 • make the cards with nice pictures, remove the onex@onex.am thing from the cards, make only ONEX maybe
@@ -3071,12 +3074,12 @@
       </c>
     </row>
     <row r="203" ht="86.40000000000001" customHeight="1">
-      <c r="A203" s="2" t="inlineStr">
+      <c r="A203" s="3" t="inlineStr">
         <is>
           <t>24/09/2026 17:59:13</t>
         </is>
       </c>
-      <c r="B203" s="3" t="inlineStr">
+      <c r="B203" s="4" t="inlineStr">
         <is>
           <t>[ONEX-Academy]
 • add new "customized quiz" specifically designed for one concrete agent.
@@ -3087,12 +3090,12 @@
       </c>
     </row>
     <row r="204" ht="72" customHeight="1">
-      <c r="A204" s="2" t="inlineStr">
+      <c r="A204" s="3" t="inlineStr">
         <is>
           <t>29/09/2026 16:50:53</t>
         </is>
       </c>
-      <c r="B204" s="3" t="inlineStr">
+      <c r="B204" s="4" t="inlineStr">
         <is>
           <t>[Blot]
 • start creating blot game with right rules
@@ -3102,12 +3105,12 @@
       </c>
     </row>
     <row r="205" ht="72" customHeight="1">
-      <c r="A205" s="2" t="inlineStr">
+      <c r="A205" s="3" t="inlineStr">
         <is>
           <t>30/09/2026 17:02:49</t>
         </is>
       </c>
-      <c r="B205" s="3" t="inlineStr">
+      <c r="B205" s="4" t="inlineStr">
         <is>
           <t>[Blot]
 • update the gameplay and the score calculating system
@@ -3117,12 +3120,12 @@
       </c>
     </row>
     <row r="206" ht="72" customHeight="1">
-      <c r="A206" s="2" t="inlineStr">
+      <c r="A206" s="3" t="inlineStr">
         <is>
           <t>01/10/2026 19:03:15</t>
         </is>
       </c>
-      <c r="B206" s="3" t="inlineStr">
+      <c r="B206" s="4" t="inlineStr">
         <is>
           <t>[cc-kpi-onex]
 • continue working on project
@@ -3134,12 +3137,12 @@
       </c>
     </row>
     <row r="207" ht="259.2" customHeight="1">
-      <c r="A207" s="2" t="inlineStr">
+      <c r="A207" s="3" t="inlineStr">
         <is>
           <t>02/10/2026 19:58:55</t>
         </is>
       </c>
-      <c r="B207" s="3" t="inlineStr">
+      <c r="B207" s="4" t="inlineStr">
         <is>
           <t>[ai-agents-scores]
 • got the tasks from the quality control specialist and done them, here are what i have done:
@@ -3158,12 +3161,12 @@
       </c>
     </row>
     <row r="208" ht="409.6" customHeight="1">
-      <c r="A208" s="2" t="inlineStr">
+      <c r="A208" s="3" t="inlineStr">
         <is>
           <t>05/10/2026 18:35:51</t>
         </is>
       </c>
-      <c r="B208" s="3" t="inlineStr">
+      <c r="B208" s="4" t="inlineStr">
         <is>
           <t>[ai-agents-scores]
 1. Reviewing AI prompt improvements
@@ -3202,13 +3205,13 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+    <row r="209" ht="316.8" customHeight="1">
+      <c r="A209" s="3" t="inlineStr">
         <is>
           <t>06/10/2026 20:32:34</t>
         </is>
       </c>
-      <c r="B209" s="3" t="inlineStr">
+      <c r="B209" s="4" t="inlineStr">
         <is>
           <t>[Blot]
 • check the server's stored feedback
@@ -3228,13 +3231,13 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>07/10/2026 20:32:34</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="inlineStr">
+    <row r="210" ht="158.4" customHeight="1">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>07/10/2026 20:51:01</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
         <is>
           <t>[Blot]
 • add ai partner feature (ai agents that act like partners with user provided rules)
@@ -3242,7 +3245,9 @@
 • separate the xosal and xaxal types of rules of the ai partner , they should be separated from each other with maybe different tabs
   when user clicks to the ai partner, make that more visual and engagig, so user should know that the default is just a bot named Ani, and that the new created ai partner isnt selected automatically.
   when user selects the ai partner it isnt selecting in the game and in the game the 'Ani' plays, fix that so the ai should play using the corresponding users rules.
-  then user types rules make for the user nice items from the rules, so the rules should be separated.</t>
+  then user types rules make for the user nice items from the rules, so the rules should be separated.
+[ai-agents-scores]
+• Read Anna's feedback and make out of them xelqy glxit tasks, and start doing them</t>
         </is>
       </c>
     </row>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -3234,7 +3234,7 @@
     <row r="210" ht="158.4" customHeight="1">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026 20:51:01</t>
+          <t>07/10/2026 21:42:32</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -3247,7 +3247,11 @@
   when user selects the ai partner it isnt selecting in the game and in the game the 'Ani' plays, fix that so the ai should play using the corresponding users rules.
   then user types rules make for the user nice items from the rules, so the rules should be separated.
 [ai-agents-scores]
-• Read Anna's feedback and make out of them xelqy glxit tasks, and start doing them</t>
+• Read Anna's feedback and make out of them xelqy glxit tasks, and start doing them
+[task-report]
+• add copy button for every task report text in the main page of the ui and in teh editing window also
+  also remove the free text task report section, no needed
+  also make nice feature which will allow user to select some of the reports and copy them together.</t>
         </is>
       </c>
     </row>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B210"/>
+  <dimension ref="A1:B211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
@@ -3255,6 +3255,19 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>12/10/2026 19:05:53</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>[cc-kpi-onex]
+• improve the ui to be more close to the prototype</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -3003,7 +3003,9 @@
 [Buy For Me]
 • create an API for the BFM articule searching for integration
 [ONEX-Academy]
-• use claude design to design very nice and bomb onex-like design for onex-academy</t>
+• use claude design to design very nice and bomb onex-like design for onex-academy
+[local computer improvements]
+• make sure the vs code wsl system is by default for any actions</t>
         </is>
       </c>
     </row>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B211"/>
+  <dimension ref="A1:B212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
@@ -3270,6 +3270,19 @@
         </is>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>09/10/2026 19:43:37</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>[cc-kpi-onex]
+• make onex-hr-insighhts api for cc-kpi-onex project</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B212"/>
+  <dimension ref="A1:B213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
@@ -3283,6 +3283,22 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>13/10/2026 15:22:00</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>[cc-kpi-onex]
+• Add two secrets in Lovable → Cloud → Secrets: SUPPORT_QUALITY_API_URL and SUPPORT_QUALITY_API_KEY (the value is in the support-quality-api folder's README). Without them the sync bar shows "temporarily unavailable".
+  Apply the database change 0006_support_quality_and_agent_logins.sql. It adds the link column and changes how new accounts get a role. I added it to the migration list but couldn't confirm that Lovable runs it automatically, so check it has run before using the new screens. Until it does, saving agents will fail.
+  Turn off public sign-ups in Lovable Cloud's auth settings, and limit Google sign-in to onex.am or turn it off. Code alone can't fully block someone registering through the public API.
+  Link each agent to their HR Insights agent, then create their logins.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B213"/>
+  <dimension ref="A1:B214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
@@ -3299,6 +3299,19 @@
         </is>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:00:25</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>[cc-kpi-onex]
+• make the cc-kpi-onex website ready to use</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -3286,7 +3286,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>13/10/2026 15:22:00</t>
+          <t>13/10/2026 16:00:29</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
@@ -3295,7 +3295,9 @@
 • Add two secrets in Lovable → Cloud → Secrets: SUPPORT_QUALITY_API_URL and SUPPORT_QUALITY_API_KEY (the value is in the support-quality-api folder's README). Without them the sync bar shows "temporarily unavailable".
   Apply the database change 0006_support_quality_and_agent_logins.sql. It adds the link column and changes how new accounts get a role. I added it to the migration list but couldn't confirm that Lovable runs it automatically, so check it has run before using the new screens. Until it does, saving agents will fail.
   Turn off public sign-ups in Lovable Cloud's auth settings, and limit Google sign-in to onex.am or turn it off. Code alone can't fully block someone registering through the public API.
-  Link each agent to their HR Insights agent, then create their logins.</t>
+  Link each agent to their HR Insights agent, then create their logins.
+[ai-agents-scores]
+• Do the latest tasks Anna said to do (remove the scores label, etc..)</t>
         </is>
       </c>
     </row>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -3253,7 +3253,18 @@
 [task-report]
 • add copy button for every task report text in the main page of the ui and in teh editing window also
   also remove the free text task report section, no needed
-  also make nice feature which will allow user to select some of the reports and copy them together.</t>
+  also make nice feature which will allow user to select some of the reports and copy them together.
+[ai-agents-scores]
+• user feedback:
+  ```5 էր տվյալ թիքեթի միջին գնահատականը, երբ էս մի կրիտերիայում դարձրեցի 0 փոխվեց գլխավորը՝ 4.89/5, բայց ավելի կարևորա ոչ թե ամեն կրիտերիայի մոտ նշվի EDITED այլ թիքեթի վերջնական միջին գնահատկանինը, կարա՞նք դա էլ փոխենք
+  ```
+  make out of that a nice task
+• user gave this feedback:
+  ```
+  Կարևոր բան չեմ գրում, բայց եթե բարդ բան չի թիքեթի համարի մոտ էլ քոփիի կոճակ դնենք, սա կօգնի ավելորդ լադեսկի թաբ չբացելով մեր գնահատման հարթակում սրչ անել արդյոք էդ թիքեթը մենք գնահատել ենք, թե չէ
+  գլխավոր գնահատկանի քոփին էլ կարևոր չի, բայց որ առաջարկեցիր նշում եմ, որ հիշենք, անելուց քեզ հարմար լինի միանգամից 2 տեղ ավելացնել
+  ```
+  make out of this a nice task</t>
         </is>
       </c>
     </row>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -3264,7 +3264,9 @@
   Կարևոր բան չեմ գրում, բայց եթե բարդ բան չի թիքեթի համարի մոտ էլ քոփիի կոճակ դնենք, սա կօգնի ավելորդ լադեսկի թաբ չբացելով մեր գնահատման հարթակում սրչ անել արդյոք էդ թիքեթը մենք գնահատել ենք, թե չէ
   գլխավոր գնահատկանի քոփին էլ կարևոր չի, բայց որ առաջարկեցիր նշում եմ, որ հիշենք, անելուց քեզ հարմար լինի միանգամից 2 տեղ ավելացնել
   ```
-  make out of this a nice task</t>
+  make out of this a nice task
+[ai-agents-scores]
+• make the score and level editing function button to be more visual showing for the users so user can understand that it's editable.</t>
         </is>
       </c>
     </row>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B214"/>
+  <dimension ref="A1:B215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
@@ -3327,6 +3327,19 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>19/10/2026 15:49:12</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>[onex-hr-insights]
+• Make the team picture to be dynamically changing corresponding to the uploaded image.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -3330,13 +3330,17 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>19/10/2026 15:49:12</t>
+          <t>19/10/2026 18:33:41</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
           <t>[onex-hr-insights]
-• Make the team picture to be dynamically changing corresponding to the uploaded image.</t>
+• Make the team picture to be dynamically changing corresponding to the uploaded image.
+[onex-hr-insights]
+• IN HR COMPUTER make new api's which should send the necessary data from to the cc-kpi-onex
+[cc-kpi-onex]
+• connect and show the necessary new apis from the onex-hr-insights</t>
         </is>
       </c>
     </row>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B215"/>
+  <dimension ref="A1:B216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
@@ -3344,6 +3344,22 @@
         </is>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>20/10/2026 19:23:03</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>[cc-kpi-onex]
+• make this page's scores and editing custom for week or month (admin decides)
+  make editable each cell(each value) in the row.
+  admin should decide whether it should be weekly score inputting or monthly with ability to change to monthly updating(weekly updating is mandatory and is set by default), and user's pages should be updated (their scores, statistics etc.. every week, admin should update the scores and other numbers, values)
+• the level kpi's should be custom adjustable by admin</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B216"/>
+  <dimension ref="A1:B217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
@@ -3360,6 +3360,20 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>21/10/2026 19:59:35</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>[cc-kpi-onex]
+• pastaci amsakan zangery - missed/not missed etc. calls
+• 'Completed calls' should be got from ladesk= calls + outgoing calls</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -3370,7 +3370,10 @@
         <is>
           <t>[cc-kpi-onex]
 • pastaci amsakan zangery - missed/not missed etc. calls
-• 'Completed calls' should be got from ladesk= calls + outgoing calls</t>
+• 'Completed calls' should be got from ladesk= calls + outgoing calls
+[cc-kpi-onex]
+• chech if onex-hr-insights apis are working well
+• add 'weekly hours' (settable by admin) to the columnts in the productivity section</t>
         </is>
       </c>
     </row>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B217"/>
+  <dimension ref="A1:B218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
@@ -3377,6 +3377,36 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>22/10/2026 18:46:56</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>[cc-kpi-onex]
+• remove armenian language entirely from the website, keep only english.
+  delete the customer rating column in scorecard (screenshot provided), it is unnecessary column, no longer needed.
+  when registering new user (when cheching the checkbox from the ladesk agents list), it should be 'Desk' or 'Call/Chat' options with dropdown, and when selected call/chat it should spawn another dropdown to select one of the 3 levels, desk dont have levels.
+  call/chat same columns
+  in scorecard motivation make two sections: desk and call/chat with corresponding columns desk workers should have two columns(customer rating column removed) and the call/chat agents should have the same columns (2nd screenshot, from agent name to teamwork)
+  fix the test accounts with corresponding scores and profile, so they should have correct level showing animations, perks avialable, etc... so we can see how the uesr can see her profile page
+  in the user profile's perks section perks should be with choosing option gold/silver or other avaliable level perks, so at the top of the perks section there should be all avialable(all active achieved) levels (the levels up to user's current level(if bronze only show bronze and other non-avialables non-clickable and with a nice user friendly lock on it)) and perk options should be with Flipping option with arrow left and right (they can flip in infinite loop from the last to first, etc... you got it), and if selected e.g. silver, the silver level perks should be flipping endlessly with arrow buttons and with nice gamy smooth animations, every perk should be with its description, selecting options, etc..
+  admin should have some place to see which user selected which perk. (maybe name 'perk selections' at the top of the website, it would be one of the main sections of the website), also selected perks should be visible from any data row that admin sees for the user, like in three dots also be the "see selected perks" or something like that
+  add to perk options the free text option, so user can see some selectable options and one of them: free option (admin decides which one should it be with nice free text checkbox), and admin also can make a perk selecting, which have one and only option of free text. Users should have nice user friendly text inputting field under the perk, or it should be one of the options, user can paste there text , type something, etc...
+  in rules section's level target subsection make sure that the added rules are connected with &amp; operator, so for a specific level all criteria should match (3rd screenshot)
+  also in user profile show absence and lates numberes in that one square (4th screenshot)
+  in team section also the profiles should be separated/grouped as call/chat or desk, with corresponding subsection: desk or call/chat
+  add started working date in user profile edit window settable by admin with nice calendar day selecting feature. Also add to the level editing section a period, which will last level untill automatically changing level to the next one, so using that and seeing when the agent was started working agent gets its level automatically (admin still can edit that, and if admin edited that, there should spawn a button "automatic setting level" and a not that e.g. 'the agent is level 3 but should be 2' or 'the agent is level 1 but should be 2' based on the 'started working' date and today's calendar)
+  ask questions if you have any, make sure you understood the tasks correct.
+  delete the 'my weeks' from user profile page, user don't need to see that weekly things
+  delete 'days worked' column from any rows in data showing, no need that data.
+  remove all the week-by-week things, make the data inserting for the whole month in the productivity, and the result should be numberes of the 1st day of the month to the last day, no other month day including.
+  Do not invent anything if you have any questions or any misunderstandings, just ask me and I will answer that with that, follow-up questions you have that feature.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -3380,7 +3380,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026 18:46:56</t>
+          <t>22/10/2026 19:56:54</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
@@ -3403,7 +3403,19 @@
   delete the 'my weeks' from user profile page, user don't need to see that weekly things
   delete 'days worked' column from any rows in data showing, no need that data.
   remove all the week-by-week things, make the data inserting for the whole month in the productivity, and the result should be numberes of the 1st day of the month to the last day, no other month day including.
-  Do not invent anything if you have any questions or any misunderstandings, just ask me and I will answer that with that, follow-up questions you have that feature.</t>
+  Do not invent anything if you have any questions or any misunderstandings, just ask me and I will answer that with that, follow-up questions you have that feature.
+[ai-agents-scores]
+• ONEX KPI website updates
+  Improved the Productivity page layout and fixed squeezed table columns.
+  Added a clear Done button for missed calls, so totals update only after confirmation.
+  Updated monthly KPI calculations: completed calls, missed calls, total calls, target, and achieved KPI.
+  Added clearer messages when hours or missed calls are missing.
+  Improved the agent table with readable names, values, and responsive spacing.
+  Kept Ladesk completed calls read-only and used them for monthly productivity.
+  Updated employee levels, rewards, attendance, and profile information.
+  Removed unused weekly and daily productivity screens.
+  Improved admin controls for agents, levels, rewards, and monthly data.
+  Checked main admin pages for layout issues and visible errors.</t>
         </is>
       </c>
     </row>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B218"/>
+  <dimension ref="A1:B219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
@@ -3419,6 +3419,30 @@
         </is>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>23/10/2026 20:09:32</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>[cc-kpi-onex]
+• 1. Three Agent Role Types (Call, Chat, Desk)
+  Added Call, Chat, and Desk profile categories when creating or editing agents.
+  Isolated call grading so only Call agents are calculated in the monthly Productivity table and team targets.
+  Created the new Desk profile layout featuring Customer Feedback, Google Review Comments, and an impact overview.
+  Added clean "Coming soon" placeholders across Productivity, Scorecards, and profiles for Chat and Desk until their custom formulas and APIs are set up.
+  2. Bug Fixes &amp; Refinements
+  Fixed placeholder visibility so Chat and Desk sections only appear when agents with those roles are present.
+  Verified that October team totals, manual missed calls, and monthly target calculations run without errors.
+  3. Quality Assurance &amp; Live Deployment
+  Ran full automated test suite (all 147 tests passed) and completed TypeScript checks.
+  Performed admin verification across the Productivity, Scorecard, Levels, and Team views.
+  Published the updated build live to https://cc-kpi-onex.lovable.app.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -3380,7 +3380,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026 19:56:54</t>
+          <t>22/10/2026 20:09:43</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
@@ -3415,7 +3415,9 @@
   Updated employee levels, rewards, attendance, and profile information.
   Removed unused weekly and daily productivity screens.
   Improved admin controls for agents, levels, rewards, and monthly data.
-  Checked main admin pages for layout issues and visible errors.</t>
+  Checked main admin pages for layout issues and visible errors.
+[ai-agents-scores]
+• change the absences and lates showing in the user profile page</t>
         </is>
       </c>
     </row>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B219"/>
+  <dimension ref="A1:B220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
@@ -3445,6 +3445,19 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:47:22</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>[cc-kpi-onex]
+• Meet with Lilit Baghdasaryan and make tasks, start doing them</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B220"/>
+  <dimension ref="A1:B221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
@@ -3458,6 +3458,19 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>28/10/2026 20:02:45</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>[cc-kpi-onex]
+• get the documentation for the Lilit Baghdasaryan and make out of them tesks, and start doing them.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B221"/>
+  <dimension ref="A1:B222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
@@ -3471,6 +3471,37 @@
         </is>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>30/10/2026 19:40:12</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>[cc-kpi-onex]
+• 1. Absence &amp; Attendance Automation
+  - Replaced manual HR spreadsheets with a live monthly calendar grid tracking daily attendance per agent.
+  - Added smart status entries: Absent (excused/unexcused), Late (check-in time + minutes), Holiday, Not checked in, and Not checked out.
+  - Implemented automatic compensation calculations: &lt;5 min late is forgiven and does not affect ratings, 5-10 min late adds +30 min work-off, and &gt;10 min late adds +1 hr work-off.
+  - Added multi-cell bulk selection (both drag-to-select and Shift/Ctrl + Click) to mark holidays for multiple days in one click.
+  - Added Call, Chat, and Desk sub-tabs to view and manage attendance by department.
+  - Connected Absence directly to the Motivation Scorecard as read-only automated counts with hover source hints, and fixed background cache updates so marks stay locked and visible.
+  2. Productivity &amp; Chat KPI Engine
+  - Separated Productivity into Call and Chat tabs with matching layouts.
+  - Built Chat KPI formulas using Ladesk chats + answers with tenure-based hourly targets (Level I: 15/hr, Level II: 20/hr, Level III: 25/hr).
+  - Added inline agent editing pencil on Chat rows matching the Call section.
+  - Added quick date filters: Today, Yesterday, Last week, Last month, and Custom calendar range.
+  3. UI &amp; Experience Improvements
+  - Made the top navigation and logo sticky during vertical scrolling.
+  - Compacted late timestamps to a clean single line (e.g., Late 09:07 · 7 min) to prevent table overflow.
+  Key Skills &amp; Impact Demonstrated:
+  - Business Process Automation: Converted complex manual HR tracking and compensation rules into real-time automated workflows.
+  - Reactive Data Architecture: Unified independent data sources (Absence grid, Ladesk API, Motivation Scorecard) with protected historical state.
+  - High-Density UI Design: Built efficient data tables with drag selection, responsive filtering, and department-level segmentation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/task_reports.xlsx
+++ b/task_reports.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B222"/>
+  <dimension ref="A1:B223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="1" min="1" max="1"/>
@@ -3502,6 +3502,19 @@
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>29/10/2026 19:40:16</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>[cc-kpi-onex]
+• finish the project and show to Lilit</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
